--- a/analysis/speed_table.xlsx
+++ b/analysis/speed_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wtrem\Projects\gcodegen\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{02BA1F35-1D8E-4B2B-9F9D-A724896FA9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CE0B609B-77E1-4854-8626-EA9ECAB45898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1248" yWindow="312" windowWidth="38808" windowHeight="25380" xr2:uid="{ADBC5C8C-19C5-42FD-8CFA-181103E7F67A}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="spray_cone_angle">Model!$B$26</definedName>
     <definedName name="v_max">Model!$B$4</definedName>
     <definedName name="viscosity">Model!$B$10</definedName>
+    <definedName name="width">Model!$B$31</definedName>
     <definedName name="z_max">Model!$B$19</definedName>
     <definedName name="z_min">Model!$B$17</definedName>
   </definedNames>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>width_mm</t>
   </si>
@@ -114,6 +115,9 @@
   </si>
   <si>
     <t>s_opacity</t>
+  </si>
+  <si>
+    <t>width</t>
   </si>
 </sst>
 </file>
@@ -270,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +502,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -688,8 +698,8 @@
     <xf numFmtId="0" fontId="17" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -736,6 +746,30 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -856,30 +890,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -894,23 +904,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$30" horiz="1" max="99" min="1" val="50"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$30" horiz="1" max="99" min="1" val="74"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="v_max" horiz="1" max="24000" page="10" val="24000"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="width" horiz="1" max="30" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$8" horiz="1" max="200" min="1" page="10" val="46"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="v_max" horiz="1" max="24000" page="10" val="2871"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$11" horiz="1" max="100" min="1" page="10" val="49"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$8" horiz="1" max="200" min="1" page="10" val="149"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$22" horiz="1" max="200" min="1" page="10" val="70"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$11" horiz="1" max="100" min="1" page="10" val="51"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$22" horiz="1" max="200" min="1" page="10" val="26"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1165,6 +1179,56 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>2773680</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>167640</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1032" name="Scroll Bar 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1032"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -1172,36 +1236,38 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{312BD4EF-DE6C-4B48-B8EA-89EE2BDEED4E}" name="Table1" displayName="Table1" ref="C4:Y25" totalsRowShown="0">
   <autoFilter ref="C4:Y25" xr:uid="{312BD4EF-DE6C-4B48-B8EA-89EE2BDEED4E}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{6908DEA3-616A-4A76-9AED-33A154B8692B}" name="width_mm"/>
+    <tableColumn id="1" xr3:uid="{6908DEA3-616A-4A76-9AED-33A154B8692B}" name="width_mm">
+      <calculatedColumnFormula>width</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="2" xr3:uid="{3E49A15C-D89E-478E-80FF-54D6DF805F8D}" name="opacity"/>
-    <tableColumn id="3" xr3:uid="{B4AB4E25-73A5-42CF-8B89-3E8A124F14C4}" name="v_max" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{B4AB4E25-73A5-42CF-8B89-3E8A124F14C4}" name="v_max" dataDxfId="12">
       <calculatedColumnFormula>v_max</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D6CEE933-36F1-4282-AB40-2AE55441A8D1}" name="opacity_gamma " dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{D6CEE933-36F1-4282-AB40-2AE55441A8D1}" name="opacity_gamma " dataDxfId="13">
       <calculatedColumnFormula>opacity_gamma</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0A028DFF-12F7-40F2-A968-25A9A5414B49}" name="viscosity" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{0A028DFF-12F7-40F2-A968-25A9A5414B49}" name="viscosity" dataDxfId="14">
       <calculatedColumnFormula>viscosity</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BBE28BCC-EEE0-43D7-962D-25D899D9A6EB}" name="min_width" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{BBE28BCC-EEE0-43D7-962D-25D899D9A6EB}" name="min_width" dataDxfId="15">
       <calculatedColumnFormula>min_width</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{26F1E5F4-2133-4978-96DA-C7E5ED79CBB8}" name="max_width" dataDxfId="13">
+    <tableColumn id="7" xr3:uid="{26F1E5F4-2133-4978-96DA-C7E5ED79CBB8}" name="max_width" dataDxfId="16">
       <calculatedColumnFormula>max_width</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5FDA2A36-0F6C-4088-8A4C-83E463CF5B25}" name="z_min" dataDxfId="8">
+    <tableColumn id="8" xr3:uid="{5FDA2A36-0F6C-4088-8A4C-83E463CF5B25}" name="z_min" dataDxfId="11">
       <calculatedColumnFormula>z_min</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{708FB954-A706-4FA2-9580-26DC4B9DFCAA}" name="z_max" dataDxfId="7">
+    <tableColumn id="9" xr3:uid="{708FB954-A706-4FA2-9580-26DC4B9DFCAA}" name="z_max" dataDxfId="10">
       <calculatedColumnFormula>z_max</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BA310A85-6F3B-4C94-B001-8CECB6046815}" name="feedrate_z_exponent " dataDxfId="6">
+    <tableColumn id="10" xr3:uid="{BA310A85-6F3B-4C94-B001-8CECB6046815}" name="feedrate_z_exponent " dataDxfId="9">
       <calculatedColumnFormula>feedrate_z_exponent</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1CE0ECDF-5BCE-4A8C-8A13-F4776000FF95}" name="feedrate_floor " dataDxfId="5">
+    <tableColumn id="11" xr3:uid="{1CE0ECDF-5BCE-4A8C-8A13-F4776000FF95}" name="feedrate_floor " dataDxfId="8">
       <calculatedColumnFormula>feedrate_floor</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{48EB6188-CB55-4FA9-B7E7-554F1043F177}" name="spray_cone_angle " dataDxfId="4">
+    <tableColumn id="12" xr3:uid="{48EB6188-CB55-4FA9-B7E7-554F1043F177}" name="spray_cone_angle " dataDxfId="7">
       <calculatedColumnFormula>spray_cone_angle</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{8B8B9EB4-D59D-4911-95B0-25B9681BA29D}" name="width_eff" dataDxfId="20">
@@ -1210,31 +1276,31 @@
     <tableColumn id="15" xr3:uid="{98F7681E-5DE6-4DC6-B3DA-266BFAB12E8D}" name="cone" dataDxfId="19">
       <calculatedColumnFormula>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FEC75162-7E2A-4FB4-AE62-A588EA02DCC5}" name="z_raw" dataDxfId="18">
+    <tableColumn id="14" xr3:uid="{FEC75162-7E2A-4FB4-AE62-A588EA02DCC5}" name="z_raw" dataDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{BE77CAF6-DC0D-49E9-8527-D247E6542C02}" name="z" dataDxfId="14">
+    <tableColumn id="22" xr3:uid="{BE77CAF6-DC0D-49E9-8527-D247E6542C02}" name="z" dataDxfId="0">
       <calculatedColumnFormula>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{494471F3-00B3-48C7-9C10-97EA3178F597}" name="opacity_factor" dataDxfId="17">
+    <tableColumn id="17" xr3:uid="{494471F3-00B3-48C7-9C10-97EA3178F597}" name="opacity_factor" dataDxfId="1">
       <calculatedColumnFormula>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{23618EAE-F55F-4DCC-9A78-B33C69EA20C4}" name="s_opacity" dataDxfId="1">
+    <tableColumn id="24" xr3:uid="{23618EAE-F55F-4DCC-9A78-B33C69EA20C4}" name="s_opacity" dataDxfId="4">
       <calculatedColumnFormula>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{980892F6-B119-4600-8A60-777BE210B9C4}" name="z_factor" dataDxfId="16">
+    <tableColumn id="18" xr3:uid="{980892F6-B119-4600-8A60-777BE210B9C4}" name="z_factor" dataDxfId="18">
       <calculatedColumnFormula>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{91BEE736-2577-4BB8-AE2C-D5344AFBBC67}" name="visc_factor" dataDxfId="15">
+    <tableColumn id="21" xr3:uid="{91BEE736-2577-4BB8-AE2C-D5344AFBBC67}" name="visc_factor" dataDxfId="17">
       <calculatedColumnFormula>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{0DCA5EF1-FDD7-45E6-B783-03C6080BA6D6}" name="speed_factor" dataDxfId="0">
+    <tableColumn id="20" xr3:uid="{0DCA5EF1-FDD7-45E6-B783-03C6080BA6D6}" name="speed_factor" dataDxfId="3">
       <calculatedColumnFormula>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{53719805-1CE0-4972-9D21-0CC0200D1307}" name="feedrate" dataDxfId="3">
+    <tableColumn id="13" xr3:uid="{53719805-1CE0-4972-9D21-0CC0200D1307}" name="feedrate" dataDxfId="6">
       <calculatedColumnFormula>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{AC40DB61-EBA3-43B5-A5C0-EDEA2A7E8B63}" name="IPS" dataDxfId="2">
+    <tableColumn id="23" xr3:uid="{AC40DB61-EBA3-43B5-A5C0-EDEA2A7E8B63}" name="IPS" dataDxfId="5">
       <calculatedColumnFormula>Table1[[#This Row],[feedrate]]/1524</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1559,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE50F952-558E-40FD-B9DC-7322D9068791}">
-  <dimension ref="A4:Y60"/>
+  <dimension ref="A4:Y64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1572,7 +1638,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="10">
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -1648,22 +1714,23 @@
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E5">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F5">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G5">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H5">
         <f>min_width</f>
@@ -1671,7 +1738,7 @@
       </c>
       <c r="I5">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J5">
         <f>z_min</f>
@@ -1683,7 +1750,7 @@
       </c>
       <c r="L5">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M5">
         <f>feedrate_floor</f>
@@ -1691,71 +1758,72 @@
       </c>
       <c r="N5">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O5" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P5" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q5" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R5" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R5" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S5" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>1</v>
+        <v>0.85471502616834227</v>
       </c>
       <c r="T5" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>1</v>
+        <v>0.96222590680376896</v>
       </c>
       <c r="U5" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V5" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W5" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.11531408239023409</v>
+        <v>0.39908030001053341</v>
       </c>
       <c r="X5" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2767.5379773656182</v>
+        <v>1145.7595413302415</v>
       </c>
       <c r="Y5" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.8159698014210093</v>
+        <v>0.75181072265763882</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0.05</v>
       </c>
       <c r="E6">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F6">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H6">
         <f>min_width</f>
@@ -1763,7 +1831,7 @@
       </c>
       <c r="I6">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J6">
         <f>z_min</f>
@@ -1775,7 +1843,7 @@
       </c>
       <c r="L6">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M6">
         <f>feedrate_floor</f>
@@ -1783,51 +1851,51 @@
       </c>
       <c r="N6">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O6" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P6" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q6" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R6" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R6" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S6" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.9766812681581879</v>
+        <v>0.92642053251798118</v>
       </c>
       <c r="T6" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.98834063407909389</v>
+        <v>0.98086933845467517</v>
       </c>
       <c r="U6" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V6" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W6" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.11396959330781284</v>
+        <v>0.40681260719937612</v>
       </c>
       <c r="X6" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2735.2702393875084</v>
+        <v>1167.9589952694089</v>
       </c>
       <c r="Y6" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.7947967450049267</v>
+        <v>0.76637729348386407</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1836,25 +1904,26 @@
       </c>
       <c r="B7" s="10">
         <f>B8/100</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0.1</v>
       </c>
       <c r="E7">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F7">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G7">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H7">
         <f>min_width</f>
@@ -1862,7 +1931,7 @@
       </c>
       <c r="I7">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <f>z_min</f>
@@ -1874,7 +1943,7 @@
       </c>
       <c r="L7">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M7">
         <f>feedrate_floor</f>
@@ -1882,75 +1951,76 @@
       </c>
       <c r="N7">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O7" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P7" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q7" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R7" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R7" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S7" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.95268988530143706</v>
+        <v>0.85471502616834227</v>
       </c>
       <c r="T7" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.97634494265071847</v>
+        <v>0.96222590680376896</v>
       </c>
       <c r="U7" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V7" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W7" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.11258632115811333</v>
+        <v>0.39908030001053341</v>
       </c>
       <c r="X7" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2702.0717077947202</v>
+        <v>1145.7595413302415</v>
       </c>
       <c r="Y7" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.7730129316238321</v>
+        <v>0.75181072265763882</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="10">
-        <v>46</v>
+        <v>149</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0.15</v>
       </c>
       <c r="E8">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F8">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G8">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H8">
         <f>min_width</f>
@@ -1958,7 +2028,7 @@
       </c>
       <c r="I8">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <f>z_min</f>
@@ -1970,7 +2040,7 @@
       </c>
       <c r="L8">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M8">
         <f>feedrate_floor</f>
@@ -1978,71 +2048,72 @@
       </c>
       <c r="N8">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O8" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P8" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q8" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R8" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R8" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S8" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.92796737081946568</v>
+        <v>0.7849359122709314</v>
       </c>
       <c r="T8" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.96398368540973278</v>
+        <v>0.94408333719044213</v>
       </c>
       <c r="U8" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V8" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W8" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.11116089412217942</v>
+        <v>0.3915557238449438</v>
       </c>
       <c r="X8" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2667.861458932306</v>
+        <v>1124.1564831588337</v>
       </c>
       <c r="Y8" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.750565261766605</v>
+        <v>0.73763548763703002</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C9">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0.2</v>
       </c>
       <c r="E9">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F9">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G9">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
         <f>min_width</f>
@@ -2050,7 +2121,7 @@
       </c>
       <c r="I9">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <f>z_min</f>
@@ -2062,7 +2133,7 @@
       </c>
       <c r="L9">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M9">
         <f>feedrate_floor</f>
@@ -2070,51 +2141,51 @@
       </c>
       <c r="N9">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P9" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q9" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R9" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R9" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S9" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.9024463526359795</v>
+        <v>0.71714022085418638</v>
       </c>
       <c r="T9" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.95122317631798969</v>
+        <v>0.92645645742208849</v>
       </c>
       <c r="U9" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V9" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W9" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10968942772543283</v>
+        <v>0.3842450284911148</v>
       </c>
       <c r="X9" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2632.5462654103881</v>
+        <v>1103.1674767979905</v>
       </c>
       <c r="Y9" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.7273925626052415</v>
+        <v>0.7238631737519623</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2123,25 +2194,26 @@
       </c>
       <c r="B10" s="10">
         <f>B11/100</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0.25</v>
       </c>
       <c r="E10">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F10">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G10">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H10">
         <f>min_width</f>
@@ -2149,7 +2221,7 @@
       </c>
       <c r="I10">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <f>z_min</f>
@@ -2161,7 +2233,7 @@
       </c>
       <c r="L10">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M10">
         <f>feedrate_floor</f>
@@ -2169,75 +2241,76 @@
       </c>
       <c r="N10">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P10" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q10" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R10" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R10" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S10" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.87604856215890592</v>
+        <v>0.6513902930312403</v>
       </c>
       <c r="T10" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.93802428107945302</v>
+        <v>0.90936147618812246</v>
       </c>
       <c r="U10" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V10" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W10" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10816740923243615</v>
+        <v>0.37715493645421766</v>
       </c>
       <c r="X10" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2596.0178215784676</v>
+        <v>1082.811822560059</v>
       </c>
       <c r="Y10" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.7034237674399395</v>
+        <v>0.71050644524938256</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="10">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0.3</v>
       </c>
       <c r="E11">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F11">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G11">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H11">
         <f>min_width</f>
@@ -2245,7 +2318,7 @@
       </c>
       <c r="I11">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <f>z_min</f>
@@ -2257,7 +2330,7 @@
       </c>
       <c r="L11">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M11">
         <f>feedrate_floor</f>
@@ -2265,71 +2338,72 @@
       </c>
       <c r="N11">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P11" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q11" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R11" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R11" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S11" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.84868220956281659</v>
+        <v>0.58775465799201332</v>
       </c>
       <c r="T11" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.9243411047814083</v>
+        <v>0.89281621107792342</v>
       </c>
       <c r="U11" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V11" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W11" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10658954631344332</v>
+        <v>0.37029283752584341</v>
       </c>
       <c r="X11" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2558.1491115226395</v>
+        <v>1063.1107365366963</v>
       </c>
       <c r="Y11" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.6785755324951703</v>
+        <v>0.69757922344927581</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C12">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0.35</v>
       </c>
       <c r="E12">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F12">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G12">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H12">
         <f>min_width</f>
@@ -2337,7 +2411,7 @@
       </c>
       <c r="I12">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J12">
         <f>z_min</f>
@@ -2349,7 +2423,7 @@
       </c>
       <c r="L12">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M12">
         <f>feedrate_floor</f>
@@ -2357,51 +2431,51 @@
       </c>
       <c r="N12">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P12" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q12" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R12" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R12" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S12" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.8202384884776982</v>
+        <v>0.52630912698671595</v>
       </c>
       <c r="T12" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.91011924423884905</v>
+        <v>0.87684037301654616</v>
       </c>
       <c r="U12" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V12" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W12" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10494956551509622</v>
+        <v>0.36366690675285879</v>
       </c>
       <c r="X12" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2518.7895723623092</v>
+        <v>1044.0876892874576</v>
       </c>
       <c r="Y12" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.6527490632298616</v>
+        <v>0.6850969089812714</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2412,22 +2486,23 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0.4</v>
       </c>
       <c r="E13">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F13">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G13">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H13">
         <f>min_width</f>
@@ -2435,7 +2510,7 @@
       </c>
       <c r="I13">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J13">
         <f>z_min</f>
@@ -2447,7 +2522,7 @@
       </c>
       <c r="L13">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M13">
         <f>feedrate_floor</f>
@@ -2455,73 +2530,74 @@
       </c>
       <c r="N13">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P13" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q13" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R13" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R13" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S13" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.79058682965229876</v>
+        <v>0.46713817860669671</v>
       </c>
       <c r="T13" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.89529341482614933</v>
+        <v>0.86145592643774116</v>
       </c>
       <c r="U13" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V13" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W13" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10323993860069662</v>
+        <v>0.35728625381808221</v>
       </c>
       <c r="X13" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2477.7585264167187</v>
+        <v>1025.7688347117141</v>
       </c>
       <c r="Y13" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.6258258047353797</v>
+        <v>0.67307666319666282</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0.45</v>
       </c>
       <c r="E14">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F14">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G14">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H14">
         <f>min_width</f>
@@ -2529,7 +2605,7 @@
       </c>
       <c r="I14">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J14">
         <f>z_min</f>
@@ -2541,7 +2617,7 @@
       </c>
       <c r="L14">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M14">
         <f>feedrate_floor</f>
@@ -2549,51 +2625,51 @@
       </c>
       <c r="N14">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P14" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q14" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R14" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R14" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S14" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.7595683099184658</v>
+        <v>0.41033674335698256</v>
       </c>
       <c r="T14" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.8797841549592329</v>
+        <v>0.84668755327281542</v>
       </c>
       <c r="U14" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V14" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W14" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.10145150253059147</v>
+        <v>0.35116111547826817</v>
       </c>
       <c r="X14" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2434.8360607341951</v>
+        <v>1008.1835625381079</v>
       </c>
       <c r="Y14" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.5976614571746688</v>
+        <v>0.66153777069429653</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2601,25 +2677,26 @@
         <v>12</v>
       </c>
       <c r="B15" s="10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0.5</v>
       </c>
       <c r="E15">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F15">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G15">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H15">
         <f>min_width</f>
@@ -2627,7 +2704,7 @@
       </c>
       <c r="I15">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15">
         <f>z_min</f>
@@ -2639,7 +2716,7 @@
       </c>
       <c r="L15">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M15">
         <f>feedrate_floor</f>
@@ -2647,73 +2724,74 @@
       </c>
       <c r="N15">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O15" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P15" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q15" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R15" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R15" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S15" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.7269862586601552</v>
+        <v>0.35601254889926798</v>
       </c>
       <c r="T15" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.8634931293300776</v>
+        <v>0.83256326271380965</v>
       </c>
       <c r="U15" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V15" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W15" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>9.9572917858969628E-2</v>
+        <v>0.34530310846155055</v>
       </c>
       <c r="X15" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2389.7500286152713</v>
+        <v>991.36522439311159</v>
       </c>
       <c r="Y15" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.568077446597947</v>
+        <v>0.65050211574351158</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0.55000000000000004</v>
       </c>
       <c r="E16">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F16">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G16">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H16">
         <f>min_width</f>
@@ -2721,7 +2799,7 @@
       </c>
       <c r="I16">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16">
         <f>z_min</f>
@@ -2733,7 +2811,7 @@
       </c>
       <c r="L16">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M16">
         <f>feedrate_floor</f>
@@ -2741,51 +2819,51 @@
       </c>
       <c r="N16">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O16" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P16" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q16" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R16" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R16" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S16" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.69259245537866421</v>
+        <v>0.30428927504869596</v>
       </c>
       <c r="T16" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.8462962276893321</v>
+        <v>0.81911521151266098</v>
       </c>
       <c r="U16" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V16" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W16" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>9.7589872926311952E-2</v>
+        <v>0.33972556968405232</v>
       </c>
       <c r="X16" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2342.1569502314869</v>
+        <v>975.35211056291416</v>
       </c>
       <c r="Y16" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.5368483925403458</v>
+        <v>0.63999482320401191</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2796,22 +2874,23 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0.6</v>
       </c>
       <c r="E17">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F17">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G17">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H17">
         <f>min_width</f>
@@ -2819,7 +2898,7 @@
       </c>
       <c r="I17">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J17">
         <f>z_min</f>
@@ -2831,7 +2910,7 @@
       </c>
       <c r="L17">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M17">
         <f>feedrate_floor</f>
@@ -2839,73 +2918,74 @@
       </c>
       <c r="N17">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P17" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q17" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R17" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R17" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S17" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.65606609754433387</v>
+        <v>0.25531091794448285</v>
       </c>
       <c r="T17" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.82803304877216699</v>
+        <v>0.80638083866556554</v>
       </c>
       <c r="U17" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V17" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W17" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>9.5483871207950391E-2</v>
+        <v>0.3344440268568114</v>
       </c>
       <c r="X17" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2291.6129089908095</v>
+        <v>960.18880110590555</v>
       </c>
       <c r="Y17" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.5036830111488251</v>
+        <v>0.63004514508261522</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0.65</v>
       </c>
       <c r="E18">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F18">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G18">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H18">
         <f>min_width</f>
@@ -2913,7 +2993,7 @@
       </c>
       <c r="I18">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J18">
         <f>z_min</f>
@@ -2925,7 +3005,7 @@
       </c>
       <c r="L18">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M18">
         <f>feedrate_floor</f>
@@ -2933,51 +3013,51 @@
       </c>
       <c r="N18">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P18" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q18" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R18" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R18" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S18" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.61698030432150586</v>
+        <v>0.20924803391915414</v>
       </c>
       <c r="T18" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.80849015216075293</v>
+        <v>0.79440448881898007</v>
       </c>
       <c r="U18" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V18" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W18" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>9.3230300017957971E-2</v>
+        <v>0.3294768717885358</v>
       </c>
       <c r="X18" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2237.5272004309913</v>
+        <v>945.92809890488627</v>
       </c>
       <c r="Y18" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.4681937010702042</v>
+        <v>0.62068772894021407</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2988,22 +3068,23 @@
         <v>83</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0.7</v>
       </c>
       <c r="E19">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F19">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G19">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H19">
         <f>min_width</f>
@@ -3011,7 +3092,7 @@
       </c>
       <c r="I19">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <f>z_min</f>
@@ -3023,7 +3104,7 @@
       </c>
       <c r="L19">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M19">
         <f>feedrate_floor</f>
@@ -3031,73 +3112,74 @@
       </c>
       <c r="N19">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P19" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q19" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R19" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R19" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S19" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.57474576143491818</v>
+        <v>0.16630705365393161</v>
       </c>
       <c r="T19" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.78737288071745914</v>
+        <v>0.78323983395002217</v>
       </c>
       <c r="U19" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V19" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W19" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>9.079518123888905E-2</v>
+        <v>0.32484636477026402</v>
       </c>
       <c r="X19" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2179.0843497333371</v>
+        <v>932.63391325542796</v>
       </c>
       <c r="Y19" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.4298453738407724</v>
+        <v>0.61196451001012331</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
       <c r="C20">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0.75</v>
       </c>
       <c r="E20">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F20">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G20">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H20">
         <f>min_width</f>
@@ -3105,7 +3187,7 @@
       </c>
       <c r="I20">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20">
         <f>z_min</f>
@@ -3117,7 +3199,7 @@
       </c>
       <c r="L20">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M20">
         <f>feedrate_floor</f>
@@ -3125,51 +3207,51 @@
       </c>
       <c r="N20">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O20" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P20" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q20" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R20" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R20" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S20" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.52850902028069013</v>
+        <v>0.12674493497375366</v>
       </c>
       <c r="T20" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.76425451014034507</v>
+        <v>0.77295368309317591</v>
       </c>
       <c r="U20" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V20" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W20" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>8.812930754943174E-2</v>
+        <v>0.32058021464805475</v>
       </c>
       <c r="X20" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2115.1033811863617</v>
+        <v>920.38579625456521</v>
       </c>
       <c r="Y20" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.3878631110146731</v>
+        <v>0.60392768783107953</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3178,25 +3260,26 @@
       </c>
       <c r="B21" s="10">
         <f>B22/100</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0.8</v>
       </c>
       <c r="E21">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F21">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G21">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H21">
         <f>min_width</f>
@@ -3204,7 +3287,7 @@
       </c>
       <c r="I21">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J21">
         <f>z_min</f>
@@ -3216,7 +3299,7 @@
       </c>
       <c r="L21">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M21">
         <f>feedrate_floor</f>
@@ -3224,75 +3307,76 @@
       </c>
       <c r="N21">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O21" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P21" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q21" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R21" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R21" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S21" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.47695103768752378</v>
+        <v>9.0893890659227164E-2</v>
       </c>
       <c r="T21" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.73847551884376195</v>
+        <v>0.76363241157139905</v>
       </c>
       <c r="U21" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V21" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W21" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>8.5156626823120432E-2</v>
+        <v>0.31671424532724646</v>
       </c>
       <c r="X21" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>2043.7590437548904</v>
+        <v>909.28659833452457</v>
       </c>
       <c r="Y21" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.3410492413089832</v>
+        <v>0.59664474956333635</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="10">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0.85</v>
       </c>
       <c r="E22">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F22">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G22">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H22">
         <f>min_width</f>
@@ -3300,7 +3384,7 @@
       </c>
       <c r="I22">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J22">
         <f>z_min</f>
@@ -3312,7 +3396,7 @@
       </c>
       <c r="L22">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M22">
         <f>feedrate_floor</f>
@@ -3320,71 +3404,72 @@
       </c>
       <c r="N22">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O22" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P22" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q22" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R22" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R22" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S22" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.41783227078635338</v>
+        <v>5.9207398071263524E-2</v>
       </c>
       <c r="T22" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.70891613539317666</v>
+        <v>0.75539392349852852</v>
       </c>
       <c r="U22" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V22" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W22" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>8.1748013644495118E-2</v>
+        <v>0.31329735718434082</v>
       </c>
       <c r="X22" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1961.9523274678829</v>
+        <v>899.47671247624248</v>
       </c>
       <c r="Y22" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.2873702936140965</v>
+        <v>0.59020781658546095</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C23">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0.9</v>
       </c>
       <c r="E23">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F23">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G23">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H23">
         <f>min_width</f>
@@ -3392,7 +3477,7 @@
       </c>
       <c r="I23">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J23">
         <f>z_min</f>
@@ -3404,7 +3489,7 @@
       </c>
       <c r="L23">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M23">
         <f>feedrate_floor</f>
@@ -3412,51 +3497,51 @@
       </c>
       <c r="N23">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O23" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P23" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q23" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R23" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R23" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S23" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.34673685045253161</v>
+        <v>3.2359365692962813E-2</v>
       </c>
       <c r="T23" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.67336842522626583</v>
+        <v>0.74841343508017033</v>
       </c>
       <c r="U23" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V23" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W23" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>7.7648862065523808E-2</v>
+        <v>0.31040222061347883</v>
       </c>
       <c r="X23" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1863.5726895725713</v>
+        <v>891.16477538129777</v>
       </c>
       <c r="Y23" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.2228167254413198</v>
+        <v>0.58475378962027413</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3467,22 +3552,23 @@
         <v>20</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0.95</v>
       </c>
       <c r="E24">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F24">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G24">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H24">
         <f>min_width</f>
@@ -3490,7 +3576,7 @@
       </c>
       <c r="I24">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24">
         <f>z_min</f>
@@ -3502,7 +3588,7 @@
       </c>
       <c r="L24">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M24">
         <f>feedrate_floor</f>
@@ -3510,73 +3596,74 @@
       </c>
       <c r="N24">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O24" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P24" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q24" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R24" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R24" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S24" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0.25207292565009182</v>
+        <v>1.1520340261115244E-2</v>
       </c>
       <c r="T24" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.62603646282504588</v>
+        <v>0.74299528846788998</v>
       </c>
       <c r="U24" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V24" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W24" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>7.2190820253498059E-2</v>
+        <v>0.30815506060641529</v>
       </c>
       <c r="X24" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1732.5796860839534</v>
+        <v>884.71317900101826</v>
       </c>
       <c r="Y24" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>1.1368633110787096</v>
+        <v>0.58052045866208546</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="10"/>
       <c r="C25">
-        <v>10</v>
+        <f>width</f>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E25">
         <f>v_max</f>
-        <v>24000</v>
+        <v>2871</v>
       </c>
       <c r="F25">
         <f>opacity_gamma</f>
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="G25">
         <f>viscosity</f>
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H25">
         <f>min_width</f>
@@ -3584,7 +3671,7 @@
       </c>
       <c r="I25">
         <f>max_width</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J25">
         <f>z_min</f>
@@ -3596,7 +3683,7 @@
       </c>
       <c r="L25">
         <f>feedrate_z_exponent</f>
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="M25">
         <f>feedrate_floor</f>
@@ -3604,51 +3691,51 @@
       </c>
       <c r="N25">
         <f>spray_cone_angle</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O25" s="1">
         <f>MIN(MAX(Table1[[#This Row],[width_mm]],Table1[[#This Row],[min_width]]),Table1[[#This Row],[max_width]])</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P25" s="1">
         <f>TAN(RADIANS(Table1[[#This Row],[spray_cone_angle ]]/2))</f>
-        <v>0.14945100134912781</v>
+        <v>0.13165249758739583</v>
       </c>
       <c r="Q25" s="1">
         <f>Table1[[#This Row],[width_eff]]/(2 * Table1[[#This Row],[cone]])</f>
-        <v>33.455781191587043</v>
-      </c>
-      <c r="R25" s="1">
+        <v>7.5957541127251513</v>
+      </c>
+      <c r="R25" s="12">
         <f>MIN(MAX(Table1[[#This Row],[z_raw]],Table1[[#This Row],[z_min]]),Table1[[#This Row],[z_max]])</f>
-        <v>33.455781191587043</v>
+        <v>7.5957541127251513</v>
       </c>
       <c r="S25" s="1">
         <f>(1-Table1[[#This Row],[opacity]])^Table1[[#This Row],[opacity_gamma ]]</f>
-        <v>0</v>
+        <v>1.0471285480509005E-3</v>
       </c>
       <c r="T25" s="1">
         <f>opacity_speed_min + (1-Table1[[#This Row],[opacity]])^opacity_gamma*(1-opacity_speed_min)</f>
-        <v>0.5</v>
+        <v>0.74027225342249325</v>
       </c>
       <c r="U25" s="1">
         <f>(Table1[[#This Row],[z_min]]/Table1[[#This Row],[z]])^Table1[[#This Row],[feedrate_z_exponent ]]</f>
-        <v>0.22610604390241978</v>
+        <v>0.84642243167573095</v>
       </c>
       <c r="V25" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="W25" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>5.7657041195117047E-2</v>
+        <v>0.30702569001353042</v>
       </c>
       <c r="X25" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1383.7689886828091</v>
+        <v>881.47075602884581</v>
       </c>
       <c r="Y25" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.90798490071050464</v>
+        <v>0.57839288453336335</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -3656,7 +3743,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
@@ -3664,12 +3751,12 @@
       <c r="B27" s="10"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="10">
         <f>B30/100</f>
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
@@ -3679,12 +3766,16 @@
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="10">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
@@ -3749,7 +3840,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C36" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f>_xlfn.LET(
@@ -3761,7 +3852,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.470045089261907</v>
+        <v>0.75181072265763882</v>
       </c>
       <c r="E36">
         <f>_xlfn.LET(
@@ -3773,7 +3864,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.329298526690641</v>
+        <v>0.7238631737519623</v>
       </c>
       <c r="F36">
         <f>_xlfn.LET(
@@ -3785,7 +3876,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.1786897234139602</v>
+        <v>0.69757922344927581</v>
       </c>
       <c r="G36">
         <f>_xlfn.LET(
@@ -3797,7 +3888,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.0159478820286969</v>
+        <v>0.67307666319666282</v>
       </c>
       <c r="H36">
         <f>_xlfn.LET(
@@ -3809,7 +3900,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.8377844195923041</v>
+        <v>0.65050211574351158</v>
       </c>
       <c r="I36">
         <f>_xlfn.LET(
@@ -3821,7 +3912,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.6391166833780737</v>
+        <v>0.63004514508261522</v>
       </c>
       <c r="J36">
         <f>_xlfn.LET(
@@ -3833,7 +3924,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.4113150705665403</v>
+        <v>0.61196451001012331</v>
       </c>
       <c r="K36">
         <f>_xlfn.LET(
@@ -3845,7 +3936,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.1373639673131013</v>
+        <v>0.59664474956333635</v>
       </c>
       <c r="L36">
         <f>_xlfn.LET(
@@ -3857,7 +3948,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.7725966374884545</v>
+        <v>0.58475378962027413</v>
       </c>
       <c r="M36">
         <f>_xlfn.LET(
@@ -3869,12 +3960,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8417780714848182</v>
+        <v>0.57818038899420998</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C37" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
         <f>_xlfn.LET(
@@ -3886,7 +3977,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.470045089261907</v>
+        <v>0.67658877477146195</v>
       </c>
       <c r="E37">
         <f>_xlfn.LET(
@@ -3898,7 +3989,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.329298526690641</v>
+        <v>0.6514375002523729</v>
       </c>
       <c r="F37">
         <f>_xlfn.LET(
@@ -3910,7 +4001,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.1786897234139602</v>
+        <v>0.6277833740268457</v>
       </c>
       <c r="G37">
         <f>_xlfn.LET(
@@ -3922,7 +4013,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>5.0159478820286969</v>
+        <v>0.60573240199298595</v>
       </c>
       <c r="H37">
         <f>_xlfn.LET(
@@ -3934,7 +4025,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.8377844195923041</v>
+        <v>0.58541653665342885</v>
       </c>
       <c r="I37">
         <f>_xlfn.LET(
@@ -3946,7 +4037,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.6391166833780737</v>
+        <v>0.56700637529517606</v>
       </c>
       <c r="J37">
         <f>_xlfn.LET(
@@ -3958,7 +4049,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.4113150705665403</v>
+        <v>0.55073478676616028</v>
       </c>
       <c r="K37">
         <f>_xlfn.LET(
@@ -3970,7 +4061,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.1373639673131013</v>
+        <v>0.53694783529273182</v>
       </c>
       <c r="L37">
         <f>_xlfn.LET(
@@ -3982,7 +4073,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.7725966374884545</v>
+        <v>0.52624661785027116</v>
       </c>
       <c r="M37">
         <f>_xlfn.LET(
@@ -3994,12 +4085,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8417780714848182</v>
+        <v>0.52033091467973247</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C38" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <f>_xlfn.LET(
@@ -4011,7 +4102,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.118385772245837</v>
+        <v>0.62782805218810633</v>
       </c>
       <c r="E38">
         <f>_xlfn.LET(
@@ -4023,7 +4114,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>4.0124179728352072</v>
+        <v>0.60448939171934257</v>
       </c>
       <c r="F38">
         <f>_xlfn.LET(
@@ -4035,7 +4126,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.8990249125463112</v>
+        <v>0.58253998234671334</v>
       </c>
       <c r="G38">
         <f>_xlfn.LET(
@@ -4047,7 +4138,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.7764969126536094</v>
+        <v>0.56207819028469042</v>
       </c>
       <c r="H38">
         <f>_xlfn.LET(
@@ -4059,7 +4150,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.6423580057783269</v>
+        <v>0.5432264584200015</v>
       </c>
       <c r="I38">
         <f>_xlfn.LET(
@@ -4071,7 +4162,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.492781473066533</v>
+        <v>0.52614308935298626</v>
       </c>
       <c r="J38">
         <f>_xlfn.LET(
@@ -4083,7 +4174,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.321270104185976</v>
+        <v>0.5110441694283554</v>
       </c>
       <c r="K38">
         <f>_xlfn.LET(
@@ -4095,7 +4186,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.115012878236445</v>
+        <v>0.49825082255070696</v>
       </c>
       <c r="L38">
         <f>_xlfn.LET(
@@ -4107,7 +4198,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8403803008416162</v>
+        <v>0.48832082555184919</v>
       </c>
       <c r="M38">
         <f>_xlfn.LET(
@@ -4119,12 +4210,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.1395689041865813</v>
+        <v>0.48283145809946015</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <f>_xlfn.LET(
@@ -4136,7 +4227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.3672077261947955</v>
+        <v>0.59243964532334925</v>
       </c>
       <c r="E39">
         <f>_xlfn.LET(
@@ -4148,7 +4239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.2805680540912387</v>
+        <v>0.57041650111651176</v>
       </c>
       <c r="F39">
         <f>_xlfn.LET(
@@ -4160,7 +4251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.1878574607139138</v>
+        <v>0.54970430092339062</v>
       </c>
       <c r="G39">
         <f>_xlfn.LET(
@@ -4172,7 +4263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>3.0876781062944483</v>
+        <v>0.53039586640910585</v>
       </c>
       <c r="H39">
         <f>_xlfn.LET(
@@ -4184,7 +4275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.9780056305740721</v>
+        <v>0.51260673879570484</v>
       </c>
       <c r="I39">
         <f>_xlfn.LET(
@@ -4196,7 +4287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8557112937980569</v>
+        <v>0.49648629773590008</v>
       </c>
       <c r="J39">
         <f>_xlfn.LET(
@@ -4208,7 +4299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.7154829523161155</v>
+        <v>0.48223844956515</v>
       </c>
       <c r="K39">
         <f>_xlfn.LET(
@@ -4220,7 +4311,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.5468462671660412</v>
+        <v>0.47016621758972721</v>
       </c>
       <c r="L39">
         <f>_xlfn.LET(
@@ -4232,7 +4323,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.3223056370238635</v>
+        <v>0.46079593876965524</v>
       </c>
       <c r="M39">
         <f>_xlfn.LET(
@@ -4244,12 +4335,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7493195983373122</v>
+        <v>0.45561598719659541</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <f>_xlfn.LET(
@@ -4261,7 +4352,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8802680049641043</v>
+        <v>0.56501111223248979</v>
       </c>
       <c r="E40">
         <f>_xlfn.LET(
@@ -4273,7 +4364,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.8061574968480922</v>
+        <v>0.54400758672337191</v>
       </c>
       <c r="F40">
         <f>_xlfn.LET(
@@ -4285,7 +4376,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.7268539974682926</v>
+        <v>0.52425431166780034</v>
       </c>
       <c r="G40">
         <f>_xlfn.LET(
@@ -4297,7 +4388,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.6411618119082343</v>
+        <v>0.50583981131067135</v>
       </c>
       <c r="H40">
         <f>_xlfn.LET(
@@ -4309,7 +4400,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.5473493273426988</v>
+        <v>0.4888742775928735</v>
       </c>
       <c r="I40">
         <f>_xlfn.LET(
@@ -4321,7 +4412,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.4427402583315865</v>
+        <v>0.47350017424786978</v>
       </c>
       <c r="J40">
         <f>_xlfn.LET(
@@ -4333,7 +4424,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.3227906626420896</v>
+        <v>0.45991196723737943</v>
       </c>
       <c r="K40">
         <f>_xlfn.LET(
@@ -4345,7 +4436,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.1785409197698669</v>
+        <v>0.44839865061617429</v>
       </c>
       <c r="L40">
         <f>_xlfn.LET(
@@ -4357,7 +4448,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.9864716310883939</v>
+        <v>0.43946219320679908</v>
       </c>
       <c r="M40">
         <f>_xlfn.LET(
@@ -4369,12 +4460,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4963464327879534</v>
+        <v>0.43452206095415824</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <f>_xlfn.LET(
@@ -4386,7 +4477,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.5351638177498264</v>
+        <v>0.54281372970546604</v>
       </c>
       <c r="E41">
         <f>_xlfn.LET(
@@ -4398,7 +4489,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.4699329856304</v>
+        <v>0.52263536193227278</v>
       </c>
       <c r="F41">
         <f>_xlfn.LET(
@@ -4410,7 +4501,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.400131369287021</v>
+        <v>0.50365812648561714</v>
       </c>
       <c r="G41">
         <f>_xlfn.LET(
@@ -4422,7 +4513,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.324706538013908</v>
+        <v>0.48596706979113768</v>
       </c>
       <c r="H41">
         <f>_xlfn.LET(
@@ -4434,7 +4525,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.242134355108059</v>
+        <v>0.46966805471970968</v>
       </c>
       <c r="I41">
         <f>_xlfn.LET(
@@ -4446,7 +4537,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.1500591988002449</v>
+        <v>0.45489794808480705</v>
       </c>
       <c r="J41">
         <f>_xlfn.LET(
@@ -4458,7 +4549,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.0444815669890266</v>
+        <v>0.44184357593585855</v>
       </c>
       <c r="K41">
         <f>_xlfn.LET(
@@ -4470,7 +4561,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.9175153512691341</v>
+        <v>0.43078257872512626</v>
       </c>
       <c r="L41">
         <f>_xlfn.LET(
@@ -4482,7 +4573,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7484591695780543</v>
+        <v>0.42219720461173893</v>
       </c>
       <c r="M41">
         <f>_xlfn.LET(
@@ -4494,12 +4585,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3170591516779075</v>
+        <v>0.41745115350718853</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C42" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <f>_xlfn.LET(
@@ -4511,7 +4602,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.2758481166599398</v>
+        <v>0.52429162186053135</v>
       </c>
       <c r="E42">
         <f>_xlfn.LET(
@@ -4523,7 +4614,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.21728958667945</v>
+        <v>0.50480178844742629</v>
       </c>
       <c r="F42">
         <f>_xlfn.LET(
@@ -4535,7 +4626,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.1546278068044522</v>
+        <v>0.48647210184175599</v>
       </c>
       <c r="G42">
         <f>_xlfn.LET(
@@ -4547,7 +4638,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.0869179968898144</v>
+        <v>0.46938470648090519</v>
       </c>
       <c r="H42">
         <f>_xlfn.LET(
@@ -4559,7 +4650,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.0127919204449509</v>
+        <v>0.45364185294040055</v>
       </c>
       <c r="I42">
         <f>_xlfn.LET(
@@ -4571,7 +4662,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.930134906485079</v>
+        <v>0.43937573780939987</v>
       </c>
       <c r="J42">
         <f>_xlfn.LET(
@@ -4583,7 +4674,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.8353565521883355</v>
+        <v>0.42676681218392443</v>
       </c>
       <c r="K42">
         <f>_xlfn.LET(
@@ -4595,7 +4686,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7213773998738198</v>
+        <v>0.41608324275734349</v>
       </c>
       <c r="L42">
         <f>_xlfn.LET(
@@ -4607,7 +4698,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5696135611752782</v>
+        <v>0.40779082222363738</v>
       </c>
       <c r="M42">
         <f>_xlfn.LET(
@@ -4619,12 +4710,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1823403950819933</v>
+        <v>0.40320671777884398</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C43" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43">
         <f>_xlfn.LET(
@@ -4636,7 +4727,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.0727594903382807</v>
+        <v>0.50847928160200628</v>
       </c>
       <c r="E43">
         <f>_xlfn.LET(
@@ -4648,7 +4739,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>2.0194265161961158</v>
+        <v>0.48957725059630258</v>
       </c>
       <c r="F43">
         <f>_xlfn.LET(
@@ -4660,7 +4751,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.9623564516489229</v>
+        <v>0.4718003770232197</v>
       </c>
       <c r="G43">
         <f>_xlfn.LET(
@@ -4672,7 +4763,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.9006888253859102</v>
+        <v>0.45522832789014001</v>
       </c>
       <c r="H43">
         <f>_xlfn.LET(
@@ -4684,7 +4775,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.8331774974954866</v>
+        <v>0.43996026995277548</v>
       </c>
       <c r="I43">
         <f>_xlfn.LET(
@@ -4696,7 +4787,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7578965027427302</v>
+        <v>0.42612441282555169</v>
       </c>
       <c r="J43">
         <f>_xlfn.LET(
@@ -4708,7 +4799,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6715758331386728</v>
+        <v>0.41389576530098682</v>
       </c>
       <c r="K43">
         <f>_xlfn.LET(
@@ -4720,7 +4811,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5677677767349134</v>
+        <v>0.40353440631589499</v>
       </c>
       <c r="L43">
         <f>_xlfn.LET(
@@ -4732,7 +4823,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4295468055506684</v>
+        <v>0.39549208051874096</v>
       </c>
       <c r="M43">
         <f>_xlfn.LET(
@@ -4744,12 +4835,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0768325253238775</v>
+        <v>0.3910462300841957</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C44" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <f>_xlfn.LET(
@@ -4761,7 +4852,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.9087196589712447</v>
+        <v>0.49473919079995676</v>
       </c>
       <c r="E44">
         <f>_xlfn.LET(
@@ -4773,7 +4864,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.8596074987369955</v>
+        <v>0.47634792912499802</v>
       </c>
       <c r="F44">
         <f>_xlfn.LET(
@@ -4785,7 +4876,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.8070540043987755</v>
+        <v>0.45905142095894047</v>
       </c>
       <c r="G44">
         <f>_xlfn.LET(
@@ -4797,7 +4888,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7502668030283486</v>
+        <v>0.44292718055298752</v>
       </c>
       <c r="H44">
         <f>_xlfn.LET(
@@ -4809,7 +4900,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6880983752158796</v>
+        <v>0.42807169498586672</v>
       </c>
       <c r="I44">
         <f>_xlfn.LET(
@@ -4821,7 +4912,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6187751781439188</v>
+        <v>0.41460970940096675</v>
       </c>
       <c r="J44">
         <f>_xlfn.LET(
@@ -4833,7 +4924,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5392859948513913</v>
+        <v>0.40271150351572371</v>
       </c>
       <c r="K44">
         <f>_xlfn.LET(
@@ -4845,7 +4936,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4436933904315148</v>
+        <v>0.39263012843251144</v>
       </c>
       <c r="L44">
         <f>_xlfn.LET(
@@ -4857,7 +4948,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3164113366229424</v>
+        <v>0.3848051217881937</v>
       </c>
       <c r="M44">
         <f>_xlfn.LET(
@@ -4869,12 +4960,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.9916111445085668</v>
+        <v>0.38047940680630743</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C45" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45">
         <f>_xlfn.LET(
@@ -4886,7 +4977,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7730129316238321</v>
+        <v>0.48262989148151603</v>
       </c>
       <c r="E45">
         <f>_xlfn.LET(
@@ -4898,7 +4989,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.7273925626052415</v>
+        <v>0.46468877666495706</v>
       </c>
       <c r="F45">
         <f>_xlfn.LET(
@@ -4910,7 +5001,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6785755324951703</v>
+        <v>0.44781562003126552</v>
       </c>
       <c r="G45">
         <f>_xlfn.LET(
@@ -4922,7 +5013,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6258258047353797</v>
+        <v>0.43208603858297967</v>
       </c>
       <c r="H45">
         <f>_xlfn.LET(
@@ -4934,7 +5025,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.568077446597947</v>
+        <v>0.41759415776882414</v>
       </c>
       <c r="I45">
         <f>_xlfn.LET(
@@ -4946,7 +5037,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5036830111488251</v>
+        <v>0.40446166945420198</v>
       </c>
       <c r="J45">
         <f>_xlfn.LET(
@@ -4958,7 +5049,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4298453738407724</v>
+        <v>0.39285468556854203</v>
       </c>
       <c r="K45">
         <f>_xlfn.LET(
@@ -4970,7 +5061,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3410492413089832</v>
+        <v>0.38302006350327161</v>
       </c>
       <c r="L45">
         <f>_xlfn.LET(
@@ -4982,7 +5073,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2228167254413198</v>
+        <v>0.37538658271618719</v>
       </c>
       <c r="M45">
         <f>_xlfn.LET(
@@ -4994,12 +5085,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.92110927557774158</v>
+        <v>0.37116674448402276</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C46" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D46">
         <f>_xlfn.LET(
@@ -5011,7 +5102,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6585822892445488</v>
+        <v>0.47183395416813867</v>
       </c>
       <c r="E46">
         <f>_xlfn.LET(
@@ -5023,7 +5114,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.6159062688199621</v>
+        <v>0.45429416375006887</v>
       </c>
       <c r="F46">
         <f>_xlfn.LET(
@@ -5035,7 +5126,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5702399005098748</v>
+        <v>0.43779844238201521</v>
       </c>
       <c r="G46">
         <f>_xlfn.LET(
@@ -5047,7 +5138,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5208946517164934</v>
+        <v>0.42242071559146732</v>
       </c>
       <c r="H46">
         <f>_xlfn.LET(
@@ -5059,7 +5150,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4668733852432838</v>
+        <v>0.40825300333707976</v>
       </c>
       <c r="I46">
         <f>_xlfn.LET(
@@ -5071,7 +5162,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4066349807416327</v>
+        <v>0.39541427536162388</v>
       </c>
       <c r="J46">
         <f>_xlfn.LET(
@@ -5083,7 +5174,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3375628406943307</v>
+        <v>0.38406692784047147</v>
       </c>
       <c r="K46">
         <f>_xlfn.LET(
@@ -5095,7 +5186,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2544976299765762</v>
+        <v>0.37445229621754916</v>
       </c>
       <c r="L46">
         <f>_xlfn.LET(
@@ -5107,7 +5198,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1438958665414201</v>
+        <v>0.36698956859249382</v>
       </c>
       <c r="M46">
         <f>_xlfn.LET(
@@ -5119,12 +5210,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.86166068147789887</v>
+        <v>0.36286412382793498</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C47" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47">
         <f>_xlfn.LET(
@@ -5136,7 +5227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.560576385568434</v>
+        <v>0.46211603967890125</v>
       </c>
       <c r="E47">
         <f>_xlfn.LET(
@@ -5148,7 +5239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.5204220982975982</v>
+        <v>0.4449374996158264</v>
       </c>
       <c r="F47">
         <f>_xlfn.LET(
@@ -5160,7 +5251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4774541632958</v>
+        <v>0.42878152490711541</v>
       </c>
       <c r="G47">
         <f>_xlfn.LET(
@@ -5172,7 +5263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4310247334711121</v>
+        <v>0.4137205185065887</v>
       </c>
       <c r="H47">
         <f>_xlfn.LET(
@@ -5184,7 +5275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3801955926299971</v>
+        <v>0.3998446051254701</v>
       </c>
       <c r="I47">
         <f>_xlfn.LET(
@@ -5196,7 +5287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3235166854818843</v>
+        <v>0.3872703042000683</v>
       </c>
       <c r="J47">
         <f>_xlfn.LET(
@@ -5208,7 +5299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2585260296926002</v>
+        <v>0.37615666718642832</v>
       </c>
       <c r="K47">
         <f>_xlfn.LET(
@@ -5220,7 +5311,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1803691561090546</v>
+        <v>0.36674005897223211</v>
       </c>
       <c r="L47">
         <f>_xlfn.LET(
@@ -5232,7 +5323,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0763028692938568</v>
+        <v>0.359431034039143</v>
       </c>
       <c r="M47">
         <f>_xlfn.LET(
@@ -5244,12 +5335,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.81074500831652518</v>
+        <v>0.35539055713053835</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C48" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48">
         <f>_xlfn.LET(
@@ -5261,7 +5352,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4755419345676957</v>
+        <v>0.45329718817689096</v>
       </c>
       <c r="E48">
         <f>_xlfn.LET(
@@ -5273,7 +5364,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4375756195133931</v>
+        <v>0.43644647701571454</v>
       </c>
       <c r="F48">
         <f>_xlfn.LET(
@@ -5285,7 +5376,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3969489699477338</v>
+        <v>0.42059881695006457</v>
       </c>
       <c r="G48">
         <f>_xlfn.LET(
@@ -5297,7 +5388,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3530494394038053</v>
+        <v>0.4058252292225823</v>
       </c>
       <c r="H48">
         <f>_xlfn.LET(
@@ -5309,7 +5400,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3049899342730811</v>
+        <v>0.39221411863785194</v>
       </c>
       <c r="I48">
         <f>_xlfn.LET(
@@ -5321,7 +5412,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2513994115175762</v>
+        <v>0.37987978101837605</v>
       </c>
       <c r="J48">
         <f>_xlfn.LET(
@@ -5333,7 +5424,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1899500400808722</v>
+        <v>0.36897823254106693</v>
       </c>
       <c r="K48">
         <f>_xlfn.LET(
@@ -5345,7 +5436,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1160518666151618</v>
+        <v>0.35974132739355347</v>
       </c>
       <c r="L48">
         <f>_xlfn.LET(
@@ -5357,7 +5448,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0176560613277181</v>
+        <v>0.35257178518769072</v>
       </c>
       <c r="M48">
         <f>_xlfn.LET(
@@ -5369,12 +5460,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.76656821740688119</v>
+        <v>0.34860841524529101</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C49" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D49">
         <f>_xlfn.LET(
@@ -5386,7 +5477,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.4009488472237168</v>
+        <v>0.44523837296638263</v>
       </c>
       <c r="E49">
         <f>_xlfn.LET(
@@ -5398,7 +5489,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3649018437041316</v>
+        <v>0.42868723738377912</v>
       </c>
       <c r="F49">
         <f>_xlfn.LET(
@@ -5410,7 +5501,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3263289935924554</v>
+        <v>0.41312132043791694</v>
       </c>
       <c r="G49">
         <f>_xlfn.LET(
@@ -5422,7 +5513,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2846487164899292</v>
+        <v>0.39861038074046307</v>
       </c>
       <c r="H49">
         <f>_xlfn.LET(
@@ -5434,7 +5525,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.239018764040793</v>
+        <v>0.38524125141631205</v>
       </c>
       <c r="I49">
         <f>_xlfn.LET(
@@ -5446,7 +5537,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1881374035605587</v>
+        <v>0.37312619631217475</v>
       </c>
       <c r="J49">
         <f>_xlfn.LET(
@@ -5458,7 +5549,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1297944828613282</v>
+        <v>0.36241845791570987</v>
       </c>
       <c r="K49">
         <f>_xlfn.LET(
@@ -5470,7 +5561,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0596320845564258</v>
+        <v>0.35334576846077598</v>
       </c>
       <c r="L49">
         <f>_xlfn.LET(
@@ -5482,7 +5573,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96621048347568106</v>
+        <v>0.34630368792308142</v>
       </c>
       <c r="M49">
         <f>_xlfn.LET(
@@ -5494,12 +5585,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.72781588603860847</v>
+        <v>0.34241077962661676</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50">
         <f>_xlfn.LET(
@@ -5511,7 +5602,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3348978139031666</v>
+        <v>0.43782959967323654</v>
       </c>
       <c r="E50">
         <f>_xlfn.LET(
@@ -5523,7 +5614,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.3005503312727957</v>
+        <v>0.42155387523828103</v>
       </c>
       <c r="F50">
         <f>_xlfn.LET(
@@ -5535,7 +5626,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2637960890375197</v>
+        <v>0.40624697538697774</v>
       </c>
       <c r="G50">
         <f>_xlfn.LET(
@@ -5547,7 +5638,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2240809267763846</v>
+        <v>0.39197749794663495</v>
       </c>
       <c r="H50">
         <f>_xlfn.LET(
@@ -5559,7 +5650,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1806023059162682</v>
+        <v>0.37883083113762944</v>
       </c>
       <c r="I50">
         <f>_xlfn.LET(
@@ -5571,7 +5662,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1321198670263082</v>
+        <v>0.36691737073455644</v>
       </c>
       <c r="J50">
         <f>_xlfn.LET(
@@ -5583,7 +5674,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.076527660749492</v>
+        <v>0.3563878092677511</v>
       </c>
       <c r="K50">
         <f>_xlfn.LET(
@@ -5595,7 +5686,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0096732339793606</v>
+        <v>0.34746608950323915</v>
       </c>
       <c r="L50">
         <f>_xlfn.LET(
@@ -5607,7 +5698,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.92065621433502753</v>
+        <v>0.34054118929272137</v>
       </c>
       <c r="M50">
         <f>_xlfn.LET(
@@ -5619,12 +5710,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.69350129172973773</v>
+        <v>0.33671305904947652</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C51" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D51">
         <f>_xlfn.LET(
@@ -5636,7 +5727,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2759331333688149</v>
+        <v>0.43098245911471034</v>
       </c>
       <c r="E51">
         <f>_xlfn.LET(
@@ -5648,7 +5739,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2431028367877173</v>
+        <v>0.41496126788852195</v>
       </c>
       <c r="F51">
         <f>_xlfn.LET(
@@ -5660,7 +5751,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2079720912194623</v>
+        <v>0.39989374996771243</v>
       </c>
       <c r="G51">
         <f>_xlfn.LET(
@@ -5672,7 +5763,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1700112144404873</v>
+        <v>0.385847430390163</v>
       </c>
       <c r="H51">
         <f>_xlfn.LET(
@@ -5684,7 +5775,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1284531173555914</v>
+        <v>0.37290636200480121</v>
       </c>
       <c r="I51">
         <f>_xlfn.LET(
@@ -5696,7 +5787,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0821122292951393</v>
+        <v>0.36117921412600512</v>
       </c>
       <c r="J51">
         <f>_xlfn.LET(
@@ -5708,7 +5799,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0289756242255255</v>
+        <v>0.35081432262997536</v>
       </c>
       <c r="K51">
         <f>_xlfn.LET(
@@ -5720,7 +5811,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96507426987468425</v>
+        <v>0.34203212808097416</v>
       </c>
       <c r="L51">
         <f>_xlfn.LET(
@@ -5732,7 +5823,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.87998928163438861</v>
+        <v>0.33521552517408904</v>
       </c>
       <c r="M51">
         <f>_xlfn.LET(
@@ -5744,12 +5835,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.66286817383029495</v>
+        <v>0.3314472623904024</v>
       </c>
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C52" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52">
         <f>_xlfn.LET(
@@ -5761,7 +5852,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.2229189034271455</v>
+        <v>0.42462490534545133</v>
       </c>
       <c r="E52">
         <f>_xlfn.LET(
@@ -5773,7 +5864,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1914526852969365</v>
+        <v>0.40884004759992765</v>
       </c>
       <c r="F52">
         <f>_xlfn.LET(
@@ -5785,7 +5876,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1577816004074981</v>
+        <v>0.39399479523384073</v>
       </c>
       <c r="G52">
         <f>_xlfn.LET(
@@ -5797,7 +5888,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1213979745029747</v>
+        <v>0.38015567720263249</v>
       </c>
       <c r="H52">
         <f>_xlfn.LET(
@@ -5809,7 +5900,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0815665905640728</v>
+        <v>0.367405506466007</v>
       </c>
       <c r="I52">
         <f>_xlfn.LET(
@@ -5821,7 +5912,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0371511376468021</v>
+        <v>0.35585134932412549</v>
       </c>
       <c r="J52">
         <f>_xlfn.LET(
@@ -5833,7 +5924,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.98622232554518063</v>
+        <v>0.34563935350541375</v>
       </c>
       <c r="K52">
         <f>_xlfn.LET(
@@ -5845,7 +5936,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.92497603281515894</v>
+        <v>0.33698670778810297</v>
       </c>
       <c r="L52">
         <f>_xlfn.LET(
@@ -5857,7 +5948,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.84342627303879214</v>
+        <v>0.33027065867079253</v>
       </c>
       <c r="M52">
         <f>_xlfn.LET(
@@ -5869,12 +5960,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.6353264125346455</v>
+        <v>0.32655798268131836</v>
       </c>
     </row>
     <row r="53" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C53" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <f>_xlfn.LET(
@@ -5886,7 +5977,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1749547723920311</v>
+        <v>0.41869751000356209</v>
       </c>
       <c r="E53">
         <f>_xlfn.LET(
@@ -5898,7 +5989,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1447226915421826</v>
+        <v>0.40313299517974505</v>
       </c>
       <c r="F53">
         <f>_xlfn.LET(
@@ -5910,7 +6001,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1123722210640561</v>
+        <v>0.38849496965931934</v>
       </c>
       <c r="G53">
         <f>_xlfn.LET(
@@ -5922,7 +6013,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0774155982057092</v>
+        <v>0.37484903371121875</v>
       </c>
       <c r="H53">
         <f>_xlfn.LET(
@@ -5934,7 +6025,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0391464419118301</v>
+        <v>0.36227684429806523</v>
       </c>
       <c r="I53">
         <f>_xlfn.LET(
@@ -5946,7 +6037,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.99647300851665366</v>
+        <v>0.35088397316734349</v>
       </c>
       <c r="J53">
         <f>_xlfn.LET(
@@ -5958,7 +6049,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.94754167655068078</v>
+        <v>0.34081452795196476</v>
       </c>
       <c r="K53">
         <f>_xlfn.LET(
@@ -5970,7 +6061,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.88869752610637032</v>
+        <v>0.33228266566321446</v>
       </c>
       <c r="L53">
         <f>_xlfn.LET(
@@ -5982,7 +6073,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.81034623137362483</v>
+        <v>0.32566036676581039</v>
       </c>
       <c r="M53">
         <f>_xlfn.LET(
@@ -5994,12 +6085,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.61040826038614038</v>
+        <v>0.32199951651262476</v>
       </c>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C54" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <f>_xlfn.LET(
@@ -6011,7 +6102,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1313171805438902</v>
+        <v>0.41315072150481091</v>
       </c>
       <c r="E54">
         <f>_xlfn.LET(
@@ -6023,7 +6114,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.1022079133000158</v>
+        <v>0.39779240105700686</v>
       </c>
       <c r="F54">
         <f>_xlfn.LET(
@@ -6035,7 +6126,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0710589330068649</v>
+        <v>0.38334829603923815</v>
       </c>
       <c r="G54">
         <f>_xlfn.LET(
@@ -6047,7 +6138,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0374005923262877</v>
+        <v>0.36988313766626807</v>
       </c>
       <c r="H54">
         <f>_xlfn.LET(
@@ -6059,7 +6150,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0005527450580534</v>
+        <v>0.357477501131923</v>
       </c>
       <c r="I54">
         <f>_xlfn.LET(
@@ -6071,7 +6162,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.95946419468391975</v>
+        <v>0.34623555959845415</v>
       </c>
       <c r="J54">
         <f>_xlfn.LET(
@@ -6083,7 +6174,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.91235016287544157</v>
+        <v>0.33629951160081617</v>
       </c>
       <c r="K54">
         <f>_xlfn.LET(
@@ -6095,7 +6186,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.85569147273996626</v>
+        <v>0.32788067705759932</v>
       </c>
       <c r="L54">
         <f>_xlfn.LET(
@@ -6107,7 +6198,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.78025012986295073</v>
+        <v>0.32134610853948292</v>
       </c>
       <c r="M54">
         <f>_xlfn.LET(
@@ -6119,12 +6210,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.58773781625216248</v>
+        <v>0.31773375621521938</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C55" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55">
         <f>_xlfn.LET(
@@ -6136,7 +6227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0914174827784862</v>
+        <v>0.40794282378919366</v>
       </c>
       <c r="E55">
         <f>_xlfn.LET(
@@ -6148,7 +6239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0633348515525005</v>
+        <v>0.39277809990993617</v>
       </c>
       <c r="F55">
         <f>_xlfn.LET(
@@ -6160,7 +6251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0332844446044485</v>
+        <v>0.3785160674812027</v>
       </c>
       <c r="G55">
         <f>_xlfn.LET(
@@ -6172,7 +6263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0008131782859826</v>
+        <v>0.36522064175997665</v>
       </c>
       <c r="H55">
         <f>_xlfn.LET(
@@ -6184,7 +6275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96526489403561178</v>
+        <v>0.35297138226385311</v>
       </c>
       <c r="I55">
         <f>_xlfn.LET(
@@ -6196,7 +6287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.92562546930876877</v>
+        <v>0.34187114901887045</v>
       </c>
       <c r="J55">
         <f>_xlfn.LET(
@@ -6208,7 +6299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.88017307197557004</v>
+        <v>0.33206034810171847</v>
       </c>
       <c r="K55">
         <f>_xlfn.LET(
@@ -6220,7 +6311,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.82551264072899666</v>
+        <v>0.32374763567545228</v>
       </c>
       <c r="L55">
         <f>_xlfn.LET(
@@ -6232,7 +6323,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.75273199003590241</v>
+        <v>0.31729543749505207</v>
       </c>
       <c r="M55">
         <f>_xlfn.LET(
@@ -6244,12 +6335,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.56700926935385965</v>
+        <v>0.31372862003358387</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C56" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56">
         <f>_xlfn.LET(
@@ -6261,7 +6352,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0547715248959464</v>
+        <v>0.40373522737224987</v>
       </c>
       <c r="E56">
         <f>_xlfn.LET(
@@ -6273,7 +6364,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0276318095911154</v>
+        <v>0.38872691521085417</v>
       </c>
       <c r="F56">
         <f>_xlfn.LET(
@@ -6285,7 +6376,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.99859038954747692</v>
+        <v>0.37461198397632262</v>
       </c>
       <c r="G56">
         <f>_xlfn.LET(
@@ -6297,7 +6388,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96720939407098983</v>
+        <v>0.36145368969206315</v>
       </c>
       <c r="H56">
         <f>_xlfn.LET(
@@ -6309,7 +6400,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.93285469609534066</v>
+        <v>0.34933077128434842</v>
       </c>
       <c r="I56">
         <f>_xlfn.LET(
@@ -6321,7 +6412,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.894546223741855</v>
+        <v>0.33834502786221637</v>
       </c>
       <c r="J56">
         <f>_xlfn.LET(
@@ -6333,7 +6424,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.8506199579436694</v>
+        <v>0.32863541732856694</v>
       </c>
       <c r="K56">
         <f>_xlfn.LET(
@@ -6345,7 +6436,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.79779483160370612</v>
+        <v>0.32040844372887201</v>
       </c>
       <c r="L56">
         <f>_xlfn.LET(
@@ -6357,7 +6448,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.72745789901303159</v>
+        <v>0.31402279469301397</v>
       </c>
       <c r="M56">
         <f>_xlfn.LET(
@@ -6369,12 +6460,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.54797109364967922</v>
+        <v>0.3104927660350143</v>
       </c>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C57" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D57">
         <f>_xlfn.LET(
@@ -6386,7 +6477,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>1.0209771597381243</v>
+        <v>0.40373522737224987</v>
       </c>
       <c r="E57">
         <f>_xlfn.LET(
@@ -6398,7 +6489,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.9947069876733623</v>
+        <v>0.38872691521085417</v>
       </c>
       <c r="F57">
         <f>_xlfn.LET(
@@ -6410,7 +6501,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96659604056200454</v>
+        <v>0.37461198397632262</v>
       </c>
       <c r="G57">
         <f>_xlfn.LET(
@@ -6422,7 +6513,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.93622047687346144</v>
+        <v>0.36145368969206315</v>
       </c>
       <c r="H57">
         <f>_xlfn.LET(
@@ -6434,7 +6525,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.90296648666330692</v>
+        <v>0.34933077128434842</v>
       </c>
       <c r="I57">
         <f>_xlfn.LET(
@@ -6446,7 +6537,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.86588539907779749</v>
+        <v>0.33834502786221637</v>
       </c>
       <c r="J57">
         <f>_xlfn.LET(
@@ -6458,7 +6549,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.82336650940929068</v>
+        <v>0.32863541732856694</v>
       </c>
       <c r="K57">
         <f>_xlfn.LET(
@@ -6470,7 +6561,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.77223387435004986</v>
+        <v>0.32040844372887201</v>
       </c>
       <c r="L57">
         <f>_xlfn.LET(
@@ -6482,7 +6573,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.70415050277040558</v>
+        <v>0.31402279469301397</v>
       </c>
       <c r="M57">
         <f>_xlfn.LET(
@@ -6494,12 +6585,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.53041436710024426</v>
+        <v>0.3104927660350143</v>
       </c>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C58" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D58">
         <f>_xlfn.LET(
@@ -6511,7 +6602,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.98969737406261449</v>
+        <v>0.40373522737224987</v>
       </c>
       <c r="E58">
         <f>_xlfn.LET(
@@ -6523,7 +6614,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96423204404941765</v>
+        <v>0.38872691521085417</v>
       </c>
       <c r="F58">
         <f>_xlfn.LET(
@@ -6535,7 +6626,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.93698233501022643</v>
+        <v>0.37461198397632262</v>
       </c>
       <c r="G58">
         <f>_xlfn.LET(
@@ -6547,7 +6638,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.90753739069243777</v>
+        <v>0.36145368969206315</v>
       </c>
       <c r="H58">
         <f>_xlfn.LET(
@@ -6559,7 +6650,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.87530220651208335</v>
+        <v>0.34933077128434842</v>
       </c>
       <c r="I58">
         <f>_xlfn.LET(
@@ -6571,7 +6662,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.83935717614511829</v>
+        <v>0.33834502786221637</v>
       </c>
       <c r="J58">
         <f>_xlfn.LET(
@@ -6583,7 +6674,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.79814094221509335</v>
+        <v>0.32863541732856694</v>
       </c>
       <c r="K58">
         <f>_xlfn.LET(
@@ -6595,7 +6686,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.74857486312669053</v>
+        <v>0.32040844372887201</v>
       </c>
       <c r="L58">
         <f>_xlfn.LET(
@@ -6607,7 +6698,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.68257736903290855</v>
+        <v>0.31402279469301397</v>
       </c>
       <c r="M58">
         <f>_xlfn.LET(
@@ -6619,12 +6710,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.51416400580287469</v>
+        <v>0.3104927660350143</v>
       </c>
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C59" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59">
         <f>_xlfn.LET(
@@ -6636,7 +6727,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.96064744934528956</v>
+        <v>0.40373522737224987</v>
       </c>
       <c r="E59">
         <f>_xlfn.LET(
@@ -6648,7 +6739,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.93592958612262134</v>
+        <v>0.38872691521085417</v>
       </c>
       <c r="F59">
         <f>_xlfn.LET(
@@ -6660,7 +6751,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.90947971955740592</v>
+        <v>0.37461198397632262</v>
       </c>
       <c r="G59">
         <f>_xlfn.LET(
@@ -6672,7 +6763,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.88089905298567861</v>
+        <v>0.36145368969206315</v>
       </c>
       <c r="H59">
         <f>_xlfn.LET(
@@ -6684,7 +6775,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.84961004659484807</v>
+        <v>0.34933077128434842</v>
       </c>
       <c r="I59">
         <f>_xlfn.LET(
@@ -6696,7 +6787,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.81472008664990092</v>
+        <v>0.33834502786221637</v>
       </c>
       <c r="J59">
         <f>_xlfn.LET(
@@ -6708,7 +6799,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.77471364525260122</v>
+        <v>0.32863541732856694</v>
       </c>
       <c r="K59">
         <f>_xlfn.LET(
@@ -6720,7 +6811,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.72660244611415781</v>
+        <v>0.32040844372887201</v>
       </c>
       <c r="L59">
         <f>_xlfn.LET(
@@ -6732,7 +6823,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.66254213229911751</v>
+        <v>0.31402279469301397</v>
       </c>
       <c r="M59">
         <f>_xlfn.LET(
@@ -6744,12 +6835,12 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.49907209381808376</v>
+        <v>0.3104927660350143</v>
       </c>
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C60" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60">
         <f>_xlfn.LET(
@@ -6761,7 +6852,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.93861407216548387</v>
+        <v>0.40373522737224987</v>
       </c>
       <c r="E60">
         <f>_xlfn.LET(
@@ -6773,7 +6864,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.91446313701183324</v>
+        <v>0.38872691521085417</v>
       </c>
       <c r="F60">
         <f>_xlfn.LET(
@@ -6785,7 +6876,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.88861992368531006</v>
+        <v>0.37461198397632262</v>
       </c>
       <c r="G60">
         <f>_xlfn.LET(
@@ -6797,7 +6888,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.86069478230865237</v>
+        <v>0.36145368969206315</v>
       </c>
       <c r="H60">
         <f>_xlfn.LET(
@@ -6809,7 +6900,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.83012341950273993</v>
+        <v>0.34933077128434842</v>
       </c>
       <c r="I60">
         <f>_xlfn.LET(
@@ -6821,7 +6912,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.79603369449078432</v>
+        <v>0.33834502786221637</v>
       </c>
       <c r="J60">
         <f>_xlfn.LET(
@@ -6833,7 +6924,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.75694483947080682</v>
+        <v>0.32863541732856694</v>
       </c>
       <c r="K60">
         <f>_xlfn.LET(
@@ -6845,7 +6936,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.7099371171571992</v>
+        <v>0.32040844372887201</v>
       </c>
       <c r="L60">
         <f>_xlfn.LET(
@@ -6857,7 +6948,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.64734608851801112</v>
+        <v>0.31402279469301397</v>
       </c>
       <c r="M60">
         <f>_xlfn.LET(
@@ -6869,12 +6960,524 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48762539327200571</v>
+        <v>0.3104927660350143</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C61" s="7">
+        <v>27</v>
+      </c>
+      <c r="D61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-D$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.40373522737224987</v>
+      </c>
+      <c r="E61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-E$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.38872691521085417</v>
+      </c>
+      <c r="F61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-F$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.37461198397632262</v>
+      </c>
+      <c r="G61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-G$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.36145368969206315</v>
+      </c>
+      <c r="H61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-H$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34933077128434842</v>
+      </c>
+      <c r="I61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-I$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33834502786221637</v>
+      </c>
+      <c r="J61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-J$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32863541732856694</v>
+      </c>
+      <c r="K61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-K$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32040844372887201</v>
+      </c>
+      <c r="L61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-L$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.31402279469301397</v>
+      </c>
+      <c r="M61">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C61, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-M$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3104927660350143</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C62" s="7">
+        <v>28</v>
+      </c>
+      <c r="D62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-D$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.40373522737224987</v>
+      </c>
+      <c r="E62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-E$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.38872691521085417</v>
+      </c>
+      <c r="F62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-F$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.37461198397632262</v>
+      </c>
+      <c r="G62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-G$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.36145368969206315</v>
+      </c>
+      <c r="H62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-H$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34933077128434842</v>
+      </c>
+      <c r="I62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-I$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33834502786221637</v>
+      </c>
+      <c r="J62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-J$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32863541732856694</v>
+      </c>
+      <c r="K62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-K$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32040844372887201</v>
+      </c>
+      <c r="L62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-L$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.31402279469301397</v>
+      </c>
+      <c r="M62">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C62, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-M$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3104927660350143</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C63" s="7">
+        <v>29</v>
+      </c>
+      <c r="D63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-D$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.40373522737224987</v>
+      </c>
+      <c r="E63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-E$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.38872691521085417</v>
+      </c>
+      <c r="F63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-F$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.37461198397632262</v>
+      </c>
+      <c r="G63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-G$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.36145368969206315</v>
+      </c>
+      <c r="H63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-H$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34933077128434842</v>
+      </c>
+      <c r="I63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-I$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33834502786221637</v>
+      </c>
+      <c r="J63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-J$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32863541732856694</v>
+      </c>
+      <c r="K63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-K$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32040844372887201</v>
+      </c>
+      <c r="L63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-L$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.31402279469301397</v>
+      </c>
+      <c r="M63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-M$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3104927660350143</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C64" s="7">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-D$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.40373522737224987</v>
+      </c>
+      <c r="E64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-E$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.38872691521085417</v>
+      </c>
+      <c r="F64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-F$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.37461198397632262</v>
+      </c>
+      <c r="G64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-G$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.36145368969206315</v>
+      </c>
+      <c r="H64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-H$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34933077128434842</v>
+      </c>
+      <c r="I64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-I$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33834502786221637</v>
+      </c>
+      <c r="J64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-J$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32863541732856694</v>
+      </c>
+      <c r="K64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-K$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32040844372887201</v>
+      </c>
+      <c r="L64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-L$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.31402279469301397</v>
+      </c>
+      <c r="M64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-M$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3104927660350143</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D36:M60">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="N29:N30">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36:M64">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6915,7 +7518,29 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1026" r:id="rId4" name="Scroll Bar 2">
+            <control shapeId="1032" r:id="rId4" name="Scroll Bar 8">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>15240</xdr:colOff>
+                    <xdr:row>31</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>2773680</xdr:colOff>
+                    <xdr:row>32</xdr:row>
+                    <xdr:rowOff>167640</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1026" r:id="rId5" name="Scroll Bar 2">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6937,7 +7562,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1027" r:id="rId5" name="Scroll Bar 3">
+            <control shapeId="1027" r:id="rId6" name="Scroll Bar 3">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6959,7 +7584,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1028" r:id="rId6" name="Scroll Bar 4">
+            <control shapeId="1028" r:id="rId7" name="Scroll Bar 4">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6981,7 +7606,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1029" r:id="rId7" name="Scroll Bar 5">
+            <control shapeId="1029" r:id="rId8" name="Scroll Bar 5">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7005,7 +7630,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/analysis/speed_table.xlsx
+++ b/analysis/speed_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wtrem\Projects\gcodegen\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CE0B609B-77E1-4854-8626-EA9ECAB45898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9A8A27C2-5D9C-4F11-9BBD-7E5709408E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1248" yWindow="312" windowWidth="38808" windowHeight="25380" xr2:uid="{ADBC5C8C-19C5-42FD-8CFA-181103E7F67A}"/>
   </bookViews>
@@ -18,10 +18,15 @@
   <definedNames>
     <definedName name="feedrate_floor">Model!$B$24</definedName>
     <definedName name="feedrate_z_exponent">Model!$B$21</definedName>
+    <definedName name="flow_offset">Model!$B$42</definedName>
+    <definedName name="flow_scale">Model!$B$40</definedName>
+    <definedName name="flow_width_factor">Model!$B$38</definedName>
     <definedName name="max_width">Model!$B$15</definedName>
     <definedName name="min_width">Model!$B$13</definedName>
     <definedName name="opacity_gamma">Model!$B$7</definedName>
     <definedName name="opacity_speed_min">Model!$B$28</definedName>
+    <definedName name="p_max">Model!$B$36</definedName>
+    <definedName name="p_min">Model!$B$34</definedName>
     <definedName name="spray_cone_angle">Model!$B$26</definedName>
     <definedName name="v_max">Model!$B$4</definedName>
     <definedName name="viscosity">Model!$B$10</definedName>
@@ -33,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>width_mm</t>
   </si>
@@ -119,12 +146,30 @@
   <si>
     <t>width</t>
   </si>
+  <si>
+    <t>p_min</t>
+  </si>
+  <si>
+    <t>p_max</t>
+  </si>
+  <si>
+    <t>flow_width_factor</t>
+  </si>
+  <si>
+    <t>flow_scale</t>
+  </si>
+  <si>
+    <t>flow_offset</t>
+  </si>
+  <si>
+    <t>Flow Heatmap</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +314,13 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -680,7 +732,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -700,6 +752,8 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -908,7 +962,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="width" horiz="1" max="30" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="width" horiz="1" max="30" val="2"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -920,7 +974,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$11" horiz="1" max="100" min="1" page="10" val="51"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$11" horiz="1" max="100" min="1" page="10" val="58"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1715,7 +1769,7 @@
       <c r="B5" s="10"/>
       <c r="C5">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>0.1</v>
@@ -1730,7 +1784,7 @@
       </c>
       <c r="G5">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H5">
         <f>min_width</f>
@@ -1790,25 +1844,25 @@
       </c>
       <c r="V5" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W5" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.39908030001053341</v>
+        <v>0.34206882858045723</v>
       </c>
       <c r="X5" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1145.7595413302415</v>
+        <v>982.07960685449268</v>
       </c>
       <c r="Y5" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.75181072265763882</v>
+        <v>0.64440919084940462</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0.05</v>
@@ -1823,7 +1877,7 @@
       </c>
       <c r="G6">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H6">
         <f>min_width</f>
@@ -1883,19 +1937,19 @@
       </c>
       <c r="V6" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W6" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.40681260719937612</v>
+        <v>0.34869652045660815</v>
       </c>
       <c r="X6" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1167.9589952694089</v>
+        <v>1001.107710230922</v>
       </c>
       <c r="Y6" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.76637729348386407</v>
+        <v>0.6568948229861693</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1908,7 +1962,7 @@
       </c>
       <c r="C7">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>0.1</v>
@@ -1923,7 +1977,7 @@
       </c>
       <c r="G7">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H7">
         <f>min_width</f>
@@ -1983,19 +2037,19 @@
       </c>
       <c r="V7" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W7" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.39908030001053341</v>
+        <v>0.34206882858045723</v>
       </c>
       <c r="X7" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1145.7595413302415</v>
+        <v>982.07960685449268</v>
       </c>
       <c r="Y7" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.75181072265763882</v>
+        <v>0.64440919084940462</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2005,7 +2059,7 @@
       </c>
       <c r="C8">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>0.15</v>
@@ -2020,7 +2074,7 @@
       </c>
       <c r="G8">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H8">
         <f>min_width</f>
@@ -2080,25 +2134,25 @@
       </c>
       <c r="V8" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W8" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.3915557238449438</v>
+        <v>0.33561919186709471</v>
       </c>
       <c r="X8" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1124.1564831588337</v>
+        <v>963.56269985042888</v>
       </c>
       <c r="Y8" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.73763548763703002</v>
+        <v>0.6322589894031686</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C9">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>0.2</v>
@@ -2113,7 +2167,7 @@
       </c>
       <c r="G9">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H9">
         <f>min_width</f>
@@ -2173,19 +2227,19 @@
       </c>
       <c r="V9" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W9" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.3842450284911148</v>
+        <v>0.3293528815638127</v>
       </c>
       <c r="X9" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1103.1674767979905</v>
+        <v>945.57212296970624</v>
       </c>
       <c r="Y9" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.7238631737519623</v>
+        <v>0.62045414893025341</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2194,11 +2248,11 @@
       </c>
       <c r="B10" s="10">
         <f>B11/100</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="C10">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>0.25</v>
@@ -2213,7 +2267,7 @@
       </c>
       <c r="G10">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H10">
         <f>min_width</f>
@@ -2273,29 +2327,29 @@
       </c>
       <c r="V10" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W10" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.37715493645421766</v>
+        <v>0.32327565981790085</v>
       </c>
       <c r="X10" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1082.811822560059</v>
+        <v>928.12441933719333</v>
       </c>
       <c r="Y10" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.71050644524938256</v>
+        <v>0.60900552449947065</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="10">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>0.3</v>
@@ -2310,7 +2364,7 @@
       </c>
       <c r="G11">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H11">
         <f>min_width</f>
@@ -2370,25 +2424,25 @@
       </c>
       <c r="V11" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W11" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.37029283752584341</v>
+        <v>0.31739386073643727</v>
       </c>
       <c r="X11" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1063.1107365366963</v>
+        <v>911.23777417431143</v>
       </c>
       <c r="Y11" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.69757922344927581</v>
+        <v>0.59792504867080798</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C12">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>0.35</v>
@@ -2403,7 +2457,7 @@
       </c>
       <c r="G12">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H12">
         <f>min_width</f>
@@ -2463,19 +2517,19 @@
       </c>
       <c r="V12" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W12" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.36366690675285879</v>
+        <v>0.3117144915024504</v>
       </c>
       <c r="X12" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1044.0876892874576</v>
+        <v>894.9323051035351</v>
       </c>
       <c r="Y12" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.6850969089812714</v>
+        <v>0.58722592198394696</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2487,7 +2541,7 @@
       </c>
       <c r="C13">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0.4</v>
@@ -2502,7 +2556,7 @@
       </c>
       <c r="G13">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H13">
         <f>min_width</f>
@@ -2562,19 +2616,19 @@
       </c>
       <c r="V13" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W13" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.35728625381808221</v>
+        <v>0.30624536041549905</v>
       </c>
       <c r="X13" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1025.7688347117141</v>
+        <v>879.23042975289775</v>
       </c>
       <c r="Y13" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.67307666319666282</v>
+        <v>0.57692285416856803</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2582,7 +2636,7 @@
       <c r="B14" s="10"/>
       <c r="C14">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0.45</v>
@@ -2597,7 +2651,7 @@
       </c>
       <c r="G14">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H14">
         <f>min_width</f>
@@ -2657,19 +2711,19 @@
       </c>
       <c r="V14" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W14" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.35116111547826817</v>
+        <v>0.30099524183851561</v>
       </c>
       <c r="X14" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>1008.1835625381079</v>
+        <v>864.15733931837838</v>
       </c>
       <c r="Y14" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.66153777069429653</v>
+        <v>0.5670323748808257</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2681,7 +2735,7 @@
       </c>
       <c r="C15">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>0.5</v>
@@ -2696,7 +2750,7 @@
       </c>
       <c r="G15">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H15">
         <f>min_width</f>
@@ -2756,19 +2810,19 @@
       </c>
       <c r="V15" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W15" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.34530310846155055</v>
+        <v>0.29597409296704336</v>
       </c>
       <c r="X15" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>991.36522439311159</v>
+        <v>849.74162090838149</v>
       </c>
       <c r="Y15" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.65050211574351158</v>
+        <v>0.55757324206586711</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2776,7 +2830,7 @@
       <c r="B16" s="10"/>
       <c r="C16">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>0.55000000000000004</v>
@@ -2791,7 +2845,7 @@
       </c>
       <c r="G16">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H16">
         <f>min_width</f>
@@ -2851,19 +2905,19 @@
       </c>
       <c r="V16" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W16" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.33972556968405232</v>
+        <v>0.29119334544347347</v>
       </c>
       <c r="X16" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>975.35211056291416</v>
+        <v>836.01609476821238</v>
       </c>
       <c r="Y16" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.63999482320401191</v>
+        <v>0.54856699131772468</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2875,7 +2929,7 @@
       </c>
       <c r="C17">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -2890,7 +2944,7 @@
       </c>
       <c r="G17">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H17">
         <f>min_width</f>
@@ -2950,19 +3004,19 @@
       </c>
       <c r="V17" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W17" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.3344440268568114</v>
+        <v>0.28666630873440979</v>
       </c>
       <c r="X17" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>960.18880110590555</v>
+        <v>823.01897237649052</v>
       </c>
       <c r="Y17" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.63004514508261522</v>
+        <v>0.54003869578509878</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2970,7 +3024,7 @@
       <c r="B18" s="10"/>
       <c r="C18">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0.65</v>
@@ -2985,7 +3039,7 @@
       </c>
       <c r="G18">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H18">
         <f>min_width</f>
@@ -3045,19 +3099,19 @@
       </c>
       <c r="V18" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W18" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.3294768717885358</v>
+        <v>0.28240874724731641</v>
       </c>
       <c r="X18" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>945.92809890488627</v>
+        <v>810.79551334704536</v>
       </c>
       <c r="Y18" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.62068772894021407</v>
+        <v>0.53201805337732633</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3069,7 +3123,7 @@
       </c>
       <c r="C19">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0.7</v>
@@ -3084,7 +3138,7 @@
       </c>
       <c r="G19">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H19">
         <f>min_width</f>
@@ -3144,19 +3198,19 @@
       </c>
       <c r="V19" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W19" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.32484636477026402</v>
+        <v>0.27843974123165488</v>
       </c>
       <c r="X19" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>932.63391325542796</v>
+        <v>799.40049707608114</v>
       </c>
       <c r="Y19" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.61196451001012331</v>
+        <v>0.52454100858010577</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3164,7 +3218,7 @@
       <c r="B20" s="10"/>
       <c r="C20">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0.75</v>
@@ -3179,7 +3233,7 @@
       </c>
       <c r="G20">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H20">
         <f>min_width</f>
@@ -3239,19 +3293,19 @@
       </c>
       <c r="V20" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W20" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.32058021464805475</v>
+        <v>0.2747830411269041</v>
       </c>
       <c r="X20" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>920.38579625456521</v>
+        <v>788.90211107534174</v>
       </c>
       <c r="Y20" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.60392768783107953</v>
+        <v>0.5176523038552111</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3264,7 +3318,7 @@
       </c>
       <c r="C21">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>0.8</v>
@@ -3279,7 +3333,7 @@
       </c>
       <c r="G21">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H21">
         <f>min_width</f>
@@ -3339,19 +3393,19 @@
       </c>
       <c r="V21" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W21" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.31671424532724646</v>
+        <v>0.27146935313763981</v>
       </c>
       <c r="X21" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>909.28659833452457</v>
+        <v>779.38851285816395</v>
       </c>
       <c r="Y21" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.59664474956333635</v>
+        <v>0.51140978534000259</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3361,7 +3415,7 @@
       </c>
       <c r="C22">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>0.85</v>
@@ -3376,7 +3430,7 @@
       </c>
       <c r="G22">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H22">
         <f>min_width</f>
@@ -3436,25 +3490,25 @@
       </c>
       <c r="V22" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W22" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.31329735718434082</v>
+        <v>0.26854059187229218</v>
       </c>
       <c r="X22" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>899.47671247624248</v>
+        <v>770.9800392653508</v>
       </c>
       <c r="Y22" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.59020781658546095</v>
+        <v>0.50589241421610942</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C23">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>0.9</v>
@@ -3469,7 +3523,7 @@
       </c>
       <c r="G23">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H23">
         <f>min_width</f>
@@ -3529,19 +3583,19 @@
       </c>
       <c r="V23" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W23" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.31040222061347883</v>
+        <v>0.26605904624012472</v>
       </c>
       <c r="X23" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>891.16477538129777</v>
+        <v>763.85552175539806</v>
       </c>
       <c r="Y23" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.58475378962027413</v>
+        <v>0.50121753396023494</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3553,7 +3607,7 @@
       </c>
       <c r="C24">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>0.95</v>
@@ -3568,7 +3622,7 @@
       </c>
       <c r="G24">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H24">
         <f>min_width</f>
@@ -3628,19 +3682,19 @@
       </c>
       <c r="V24" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W24" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.30815506060641529</v>
+        <v>0.26413290909121312</v>
       </c>
       <c r="X24" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>884.71317900101826</v>
+        <v>758.32558200087283</v>
       </c>
       <c r="Y24" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.58052045866208546</v>
+        <v>0.49758896456750185</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -3648,7 +3702,7 @@
       <c r="B25" s="10"/>
       <c r="C25">
         <f>width</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>0.99</v>
@@ -3663,7 +3717,7 @@
       </c>
       <c r="G25">
         <f>viscosity</f>
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H25">
         <f>min_width</f>
@@ -3723,19 +3777,19 @@
       </c>
       <c r="V25" s="1">
         <f>MAX(0,MIN(1,1-Table1[[#This Row],[viscosity]]))</f>
-        <v>0.49</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="W25" s="1">
         <f>MAX(0,MIN(1,Table1[[#This Row],[s_opacity]]*Table1[[#This Row],[z_factor]]))*Table1[[#This Row],[visc_factor]]</f>
-        <v>0.30702569001353042</v>
+        <v>0.26316487715445469</v>
       </c>
       <c r="X25" s="2">
         <f>MAX(Table1[[#This Row],[feedrate_floor ]],Table1[[#This Row],[v_max]]*Table1[[#This Row],[speed_factor]])</f>
-        <v>881.47075602884581</v>
+        <v>755.54636231043946</v>
       </c>
       <c r="Y25" s="4">
         <f>Table1[[#This Row],[feedrate]]/1524</f>
-        <v>0.57839288453336335</v>
+        <v>0.49576532960002589</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -3774,21 +3828,30 @@
         <v>27</v>
       </c>
       <c r="B31" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="10"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" ht="21" x14ac:dyDescent="0.4">
       <c r="A33" s="9"/>
       <c r="B33" s="10"/>
-      <c r="C33" t="s">
+      <c r="C33" s="14" t="s">
         <v>22</v>
       </c>
+      <c r="O33" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="10">
+        <v>0.1</v>
+      </c>
       <c r="C34" s="5" t="s">
         <v>23</v>
       </c>
@@ -3802,8 +3865,23 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
+      <c r="O34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="6" t="s">
         <v>24</v>
       </c>
@@ -3837,8 +3915,47 @@
       <c r="M35" s="8">
         <v>0.99990000000000001</v>
       </c>
+      <c r="O35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="R35" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="S35" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="T35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U35" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="V35" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="W35" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="X35" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="Y35" s="8">
+        <v>0.99990000000000001</v>
+      </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="10">
+        <v>1</v>
+      </c>
       <c r="C36" s="7">
         <v>2</v>
       </c>
@@ -3852,7 +3969,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.75181072265763882</v>
+        <v>0.64440919084940462</v>
       </c>
       <c r="E36">
         <f>_xlfn.LET(
@@ -3864,7 +3981,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.7238631737519623</v>
+        <v>0.62045414893025341</v>
       </c>
       <c r="F36">
         <f>_xlfn.LET(
@@ -3876,7 +3993,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.69757922344927581</v>
+        <v>0.59792504867080798</v>
       </c>
       <c r="G36">
         <f>_xlfn.LET(
@@ -3888,7 +4005,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.67307666319666282</v>
+        <v>0.57692285416856803</v>
       </c>
       <c r="H36">
         <f>_xlfn.LET(
@@ -3900,7 +4017,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.65050211574351158</v>
+        <v>0.55757324206586711</v>
       </c>
       <c r="I36">
         <f>_xlfn.LET(
@@ -3912,7 +4029,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.63004514508261522</v>
+        <v>0.54003869578509878</v>
       </c>
       <c r="J36">
         <f>_xlfn.LET(
@@ -3924,7 +4041,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.61196451001012331</v>
+        <v>0.52454100858010577</v>
       </c>
       <c r="K36">
         <f>_xlfn.LET(
@@ -3936,7 +4053,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.59664474956333635</v>
+        <v>0.51140978534000259</v>
       </c>
       <c r="L36">
         <f>_xlfn.LET(
@@ -3948,7 +4065,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.58475378962027413</v>
+        <v>0.50121753396023494</v>
       </c>
       <c r="M36">
         <f>_xlfn.LET(
@@ -3960,10 +4077,135 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.57818038899420998</v>
+        <v>0.49558319056646577</v>
+      </c>
+      <c r="O36" s="7">
+        <v>2</v>
+      </c>
+      <c r="P36" cm="1">
+        <f t="array" ref="P36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.25208000000000003</v>
+      </c>
+      <c r="Q36" cm="1">
+        <f t="array" ref="Q36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.35396000000000005</v>
+      </c>
+      <c r="R36" cm="1">
+        <f t="array" ref="R36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.45584000000000002</v>
+      </c>
+      <c r="S36" cm="1">
+        <f t="array" ref="S36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.55772000000000022</v>
+      </c>
+      <c r="T36" cm="1">
+        <f t="array" ref="T36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.65960000000000019</v>
+      </c>
+      <c r="U36" cm="1">
+        <f t="array" ref="U36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.76148000000000016</v>
+      </c>
+      <c r="V36" cm="1">
+        <f t="array" ref="V36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.86336000000000013</v>
+      </c>
+      <c r="W36" cm="1">
+        <f t="array" ref="W36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.96524000000000021</v>
+      </c>
+      <c r="X36" cm="1">
+        <f t="array" ref="X36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y36" cm="1">
+        <f t="array" ref="Y36">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O36, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" s="13"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="7">
         <v>3</v>
       </c>
@@ -3977,7 +4219,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.67658877477146195</v>
+        <v>0.57993323551839615</v>
       </c>
       <c r="E37">
         <f>_xlfn.LET(
@@ -3989,7 +4231,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.6514375002523729</v>
+        <v>0.55837500021631969</v>
       </c>
       <c r="F37">
         <f>_xlfn.LET(
@@ -4001,7 +4243,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.6277833740268457</v>
+        <v>0.53810003488015345</v>
       </c>
       <c r="G37">
         <f>_xlfn.LET(
@@ -4013,7 +4255,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.60573240199298595</v>
+        <v>0.51919920170827372</v>
       </c>
       <c r="H37">
         <f>_xlfn.LET(
@@ -4025,7 +4267,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.58541653665342885</v>
+        <v>0.5017856028457961</v>
       </c>
       <c r="I37">
         <f>_xlfn.LET(
@@ -4037,7 +4279,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.56700637529517606</v>
+        <v>0.4860054645387224</v>
       </c>
       <c r="J37">
         <f>_xlfn.LET(
@@ -4049,7 +4291,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.55073478676616028</v>
+        <v>0.47205838865670868</v>
       </c>
       <c r="K37">
         <f>_xlfn.LET(
@@ -4061,7 +4303,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.53694783529273182</v>
+        <v>0.46024100167948456</v>
       </c>
       <c r="L37">
         <f>_xlfn.LET(
@@ -4073,7 +4315,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52624661785027116</v>
+        <v>0.45106852958594673</v>
       </c>
       <c r="M37">
         <f>_xlfn.LET(
@@ -4085,10 +4327,139 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52033091467973247</v>
+        <v>0.44599792686834222</v>
+      </c>
+      <c r="O37" s="7">
+        <v>3</v>
+      </c>
+      <c r="P37" cm="1">
+        <f t="array" ref="P37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.25410142857142859</v>
+      </c>
+      <c r="Q37" cm="1">
+        <f t="array" ref="Q37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.35598142857142862</v>
+      </c>
+      <c r="R37" cm="1">
+        <f t="array" ref="R37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.45786142857142859</v>
+      </c>
+      <c r="S37" cm="1">
+        <f t="array" ref="S37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.55974142857142872</v>
+      </c>
+      <c r="T37" cm="1">
+        <f t="array" ref="T37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.66162142857142869</v>
+      </c>
+      <c r="U37" cm="1">
+        <f t="array" ref="U37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.76350142857142866</v>
+      </c>
+      <c r="V37" cm="1">
+        <f t="array" ref="V37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.86538142857142863</v>
+      </c>
+      <c r="W37" cm="1">
+        <f t="array" ref="W37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.96726142857142872</v>
+      </c>
+      <c r="X37" cm="1">
+        <f t="array" ref="X37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y37" cm="1">
+        <f t="array" ref="Y37">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O37, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="10">
+        <v>0.05</v>
+      </c>
       <c r="C38" s="7">
         <v>4</v>
       </c>
@@ -4102,7 +4473,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.62782805218810633</v>
+        <v>0.53813833044694837</v>
       </c>
       <c r="E38">
         <f>_xlfn.LET(
@@ -4114,7 +4485,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.60448939171934257</v>
+        <v>0.51813376433086511</v>
       </c>
       <c r="F38">
         <f>_xlfn.LET(
@@ -4126,7 +4497,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.58253998234671334</v>
+        <v>0.49931998486861157</v>
       </c>
       <c r="G38">
         <f>_xlfn.LET(
@@ -4138,7 +4509,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.56207819028469042</v>
+        <v>0.48178130595830615</v>
       </c>
       <c r="H38">
         <f>_xlfn.LET(
@@ -4150,7 +4521,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.5432264584200015</v>
+        <v>0.46562267864571555</v>
       </c>
       <c r="I38">
         <f>_xlfn.LET(
@@ -4162,7 +4533,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52614308935298626</v>
+        <v>0.45097979087398832</v>
       </c>
       <c r="J38">
         <f>_xlfn.LET(
@@ -4174,7 +4545,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.5110441694283554</v>
+        <v>0.438037859510019</v>
       </c>
       <c r="K38">
         <f>_xlfn.LET(
@@ -4186,7 +4557,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.49825082255070696</v>
+        <v>0.42707213361489171</v>
       </c>
       <c r="L38">
         <f>_xlfn.LET(
@@ -4198,7 +4569,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48832082555184919</v>
+        <v>0.41856070761587072</v>
       </c>
       <c r="M38">
         <f>_xlfn.LET(
@@ -4210,10 +4581,135 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48283145809946015</v>
+        <v>0.41385553551382298</v>
+      </c>
+      <c r="O38" s="7">
+        <v>4</v>
+      </c>
+      <c r="P38" cm="1">
+        <f t="array" ref="P38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.25612285714285715</v>
+      </c>
+      <c r="Q38" cm="1">
+        <f t="array" ref="Q38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.35800285714285718</v>
+      </c>
+      <c r="R38" cm="1">
+        <f t="array" ref="R38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.45988285714285715</v>
+      </c>
+      <c r="S38" cm="1">
+        <f t="array" ref="S38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.56176285714285734</v>
+      </c>
+      <c r="T38" cm="1">
+        <f t="array" ref="T38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.66364285714285731</v>
+      </c>
+      <c r="U38" cm="1">
+        <f t="array" ref="U38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.76552285714285728</v>
+      </c>
+      <c r="V38" cm="1">
+        <f t="array" ref="V38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.86740285714285725</v>
+      </c>
+      <c r="W38" cm="1">
+        <f t="array" ref="W38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.96928285714285733</v>
+      </c>
+      <c r="X38" cm="1">
+        <f t="array" ref="X38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y38" cm="1">
+        <f t="array" ref="Y38">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O38, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="7">
         <v>5</v>
       </c>
@@ -4227,7 +4723,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.59243964532334925</v>
+        <v>0.50780541027715653</v>
       </c>
       <c r="E39">
         <f>_xlfn.LET(
@@ -4239,7 +4735,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.57041650111651176</v>
+        <v>0.48892842952843873</v>
       </c>
       <c r="F39">
         <f>_xlfn.LET(
@@ -4251,7 +4747,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.54970430092339062</v>
+        <v>0.47117511507719206</v>
       </c>
       <c r="G39">
         <f>_xlfn.LET(
@@ -4263,7 +4759,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.53039586640910585</v>
+        <v>0.45462502835066221</v>
       </c>
       <c r="H39">
         <f>_xlfn.LET(
@@ -4275,7 +4771,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.51260673879570484</v>
+        <v>0.43937720468203273</v>
       </c>
       <c r="I39">
         <f>_xlfn.LET(
@@ -4287,7 +4783,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.49648629773590008</v>
+        <v>0.42555968377362868</v>
       </c>
       <c r="J39">
         <f>_xlfn.LET(
@@ -4299,7 +4795,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48223844956515</v>
+        <v>0.4133472424844144</v>
       </c>
       <c r="K39">
         <f>_xlfn.LET(
@@ -4311,7 +4807,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.47016621758972721</v>
+        <v>0.40299961507690918</v>
       </c>
       <c r="L39">
         <f>_xlfn.LET(
@@ -4323,7 +4819,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.46079593876965524</v>
+        <v>0.39496794751684744</v>
       </c>
       <c r="M39">
         <f>_xlfn.LET(
@@ -4335,10 +4831,139 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45561598719659541</v>
+        <v>0.39052798902565322</v>
+      </c>
+      <c r="O39" s="7">
+        <v>5</v>
+      </c>
+      <c r="P39" cm="1">
+        <f t="array" ref="P39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.25814428571428572</v>
+      </c>
+      <c r="Q39" cm="1">
+        <f t="array" ref="Q39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.36002428571428574</v>
+      </c>
+      <c r="R39" cm="1">
+        <f t="array" ref="R39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.46190428571428571</v>
+      </c>
+      <c r="S39" cm="1">
+        <f t="array" ref="S39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.56378428571428585</v>
+      </c>
+      <c r="T39" cm="1">
+        <f t="array" ref="T39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.66566428571428582</v>
+      </c>
+      <c r="U39" cm="1">
+        <f t="array" ref="U39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.76754428571428579</v>
+      </c>
+      <c r="V39" cm="1">
+        <f t="array" ref="V39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.86942428571428576</v>
+      </c>
+      <c r="W39" cm="1">
+        <f t="array" ref="W39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.97130428571428584</v>
+      </c>
+      <c r="X39" cm="1">
+        <f t="array" ref="X39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y39" cm="1">
+        <f t="array" ref="Y39">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O39, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="10">
+        <v>1</v>
+      </c>
       <c r="C40" s="7">
         <v>6</v>
       </c>
@@ -4352,7 +4977,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.56501111223248979</v>
+        <v>0.48429523905641997</v>
       </c>
       <c r="E40">
         <f>_xlfn.LET(
@@ -4364,7 +4989,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.54400758672337191</v>
+        <v>0.46629221719146174</v>
       </c>
       <c r="F40">
         <f>_xlfn.LET(
@@ -4376,7 +5001,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52425431166780034</v>
+        <v>0.44936083857240039</v>
       </c>
       <c r="G40">
         <f>_xlfn.LET(
@@ -4388,7 +5013,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.50583981131067135</v>
+        <v>0.43357698112343263</v>
       </c>
       <c r="H40">
         <f>_xlfn.LET(
@@ -4400,7 +5025,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.4888742775928735</v>
+        <v>0.4190350950796059</v>
       </c>
       <c r="I40">
         <f>_xlfn.LET(
@@ -4412,7 +5037,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.47350017424786978</v>
+        <v>0.40585729221245986</v>
       </c>
       <c r="J40">
         <f>_xlfn.LET(
@@ -4424,7 +5049,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45991196723737943</v>
+        <v>0.3942102576320396</v>
       </c>
       <c r="K40">
         <f>_xlfn.LET(
@@ -4436,7 +5061,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.44839865061617429</v>
+        <v>0.38434170052814937</v>
       </c>
       <c r="L40">
         <f>_xlfn.LET(
@@ -4448,7 +5073,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43946219320679908</v>
+        <v>0.37668187989154206</v>
       </c>
       <c r="M40">
         <f>_xlfn.LET(
@@ -4460,10 +5085,135 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43452206095415824</v>
+        <v>0.3724474808178499</v>
+      </c>
+      <c r="O40" s="7">
+        <v>6</v>
+      </c>
+      <c r="P40" cm="1">
+        <f t="array" ref="P40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.26016571428571428</v>
+      </c>
+      <c r="Q40" cm="1">
+        <f t="array" ref="Q40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.3620457142857143</v>
+      </c>
+      <c r="R40" cm="1">
+        <f t="array" ref="R40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.46392571428571427</v>
+      </c>
+      <c r="S40" cm="1">
+        <f t="array" ref="S40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.56580571428571447</v>
+      </c>
+      <c r="T40" cm="1">
+        <f t="array" ref="T40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.66768571428571444</v>
+      </c>
+      <c r="U40" cm="1">
+        <f t="array" ref="U40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.76956571428571441</v>
+      </c>
+      <c r="V40" cm="1">
+        <f t="array" ref="V40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.87144571428571438</v>
+      </c>
+      <c r="W40" cm="1">
+        <f t="array" ref="W40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.97332571428571446</v>
+      </c>
+      <c r="X40" cm="1">
+        <f t="array" ref="X40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y40" cm="1">
+        <f t="array" ref="Y40">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O40, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="7">
         <v>7</v>
       </c>
@@ -4477,7 +5227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.54281372970546604</v>
+        <v>0.46526891117611385</v>
       </c>
       <c r="E41">
         <f>_xlfn.LET(
@@ -4489,7 +5239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52263536193227278</v>
+        <v>0.44797316737051956</v>
       </c>
       <c r="F41">
         <f>_xlfn.LET(
@@ -4501,7 +5251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.50365812648561714</v>
+        <v>0.43170696555910043</v>
       </c>
       <c r="G41">
         <f>_xlfn.LET(
@@ -4513,7 +5263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48596706979113768</v>
+        <v>0.41654320267811812</v>
       </c>
       <c r="H41">
         <f>_xlfn.LET(
@@ -4525,7 +5275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.46966805471970968</v>
+        <v>0.4025726183311798</v>
       </c>
       <c r="I41">
         <f>_xlfn.LET(
@@ -4537,7 +5287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45489794808480705</v>
+        <v>0.38991252692983469</v>
       </c>
       <c r="J41">
         <f>_xlfn.LET(
@@ -4549,7 +5299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.44184357593585855</v>
+        <v>0.37872306508787873</v>
       </c>
       <c r="K41">
         <f>_xlfn.LET(
@@ -4561,7 +5311,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43078257872512626</v>
+        <v>0.36924221033582255</v>
       </c>
       <c r="L41">
         <f>_xlfn.LET(
@@ -4573,7 +5323,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42219720461173893</v>
+        <v>0.36188331823863346</v>
       </c>
       <c r="M41">
         <f>_xlfn.LET(
@@ -4585,10 +5335,139 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41745115350718853</v>
+        <v>0.3578152744347331</v>
+      </c>
+      <c r="O41" s="7">
+        <v>7</v>
+      </c>
+      <c r="P41" cm="1">
+        <f t="array" ref="P41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.2621871428571429</v>
+      </c>
+      <c r="Q41" cm="1">
+        <f t="array" ref="Q41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.36406714285714292</v>
+      </c>
+      <c r="R41" cm="1">
+        <f t="array" ref="R41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.46594714285714289</v>
+      </c>
+      <c r="S41" cm="1">
+        <f t="array" ref="S41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.56782714285714309</v>
+      </c>
+      <c r="T41" cm="1">
+        <f t="array" ref="T41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.66970714285714295</v>
+      </c>
+      <c r="U41" cm="1">
+        <f t="array" ref="U41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.77158714285714292</v>
+      </c>
+      <c r="V41" cm="1">
+        <f t="array" ref="V41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.87346714285714289</v>
+      </c>
+      <c r="W41" cm="1">
+        <f t="array" ref="W41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.97534714285714297</v>
+      </c>
+      <c r="X41" cm="1">
+        <f t="array" ref="X41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y41" cm="1">
+        <f t="array" ref="Y41">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O41, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="10">
+        <v>0</v>
+      </c>
       <c r="C42" s="7">
         <v>8</v>
       </c>
@@ -4602,7 +5481,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.52429162186053135</v>
+        <v>0.44939281873759834</v>
       </c>
       <c r="E42">
         <f>_xlfn.LET(
@@ -4614,7 +5493,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.50480178844742629</v>
+        <v>0.43268724724065122</v>
       </c>
       <c r="F42">
         <f>_xlfn.LET(
@@ -4626,7 +5505,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48647210184175599</v>
+        <v>0.41697608729293367</v>
       </c>
       <c r="G42">
         <f>_xlfn.LET(
@@ -4638,7 +5517,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.46938470648090519</v>
+        <v>0.40232974841220448</v>
       </c>
       <c r="H42">
         <f>_xlfn.LET(
@@ -4650,7 +5529,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45364185294040055</v>
+        <v>0.38883587394891478</v>
       </c>
       <c r="I42">
         <f>_xlfn.LET(
@@ -4662,7 +5541,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43937573780939987</v>
+        <v>0.37660777526519995</v>
       </c>
       <c r="J42">
         <f>_xlfn.LET(
@@ -4674,7 +5553,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42676681218392443</v>
+        <v>0.36580012472907819</v>
       </c>
       <c r="K42">
         <f>_xlfn.LET(
@@ -4686,7 +5565,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41608324275734349</v>
+        <v>0.35664277950629447</v>
       </c>
       <c r="L42">
         <f>_xlfn.LET(
@@ -4698,7 +5577,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40779082222363738</v>
+        <v>0.3495349904774035</v>
       </c>
       <c r="M42">
         <f>_xlfn.LET(
@@ -4710,10 +5589,135 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40320671777884398</v>
+        <v>0.34560575809615196</v>
+      </c>
+      <c r="O42" s="7">
+        <v>8</v>
+      </c>
+      <c r="P42" cm="1">
+        <f t="array" ref="P42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.26420857142857146</v>
+      </c>
+      <c r="Q42" cm="1">
+        <f t="array" ref="Q42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.36608857142857149</v>
+      </c>
+      <c r="R42" cm="1">
+        <f t="array" ref="R42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.46796857142857146</v>
+      </c>
+      <c r="S42" cm="1">
+        <f t="array" ref="S42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.56984857142857159</v>
+      </c>
+      <c r="T42" cm="1">
+        <f t="array" ref="T42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.67172857142857156</v>
+      </c>
+      <c r="U42" cm="1">
+        <f t="array" ref="U42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.77360857142857153</v>
+      </c>
+      <c r="V42" cm="1">
+        <f t="array" ref="V42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.8754885714285715</v>
+      </c>
+      <c r="W42" cm="1">
+        <f t="array" ref="W42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.97736857142857159</v>
+      </c>
+      <c r="X42" cm="1">
+        <f t="array" ref="X42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y42" cm="1">
+        <f t="array" ref="Y42">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O42, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="7">
         <v>9</v>
       </c>
@@ -4727,7 +5731,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.50847928160200628</v>
+        <v>0.43583938423029123</v>
       </c>
       <c r="E43">
         <f>_xlfn.LET(
@@ -4739,7 +5743,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48957725059630258</v>
+        <v>0.41963764336825937</v>
       </c>
       <c r="F43">
         <f>_xlfn.LET(
@@ -4751,7 +5755,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.4718003770232197</v>
+        <v>0.40440032316275987</v>
       </c>
       <c r="G43">
         <f>_xlfn.LET(
@@ -4763,7 +5767,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45522832789014001</v>
+        <v>0.39019570962012001</v>
       </c>
       <c r="H43">
         <f>_xlfn.LET(
@@ -4775,7 +5779,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43996026995277548</v>
+        <v>0.37710880281666476</v>
       </c>
       <c r="I43">
         <f>_xlfn.LET(
@@ -4787,7 +5791,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42612441282555169</v>
+        <v>0.36524949670761581</v>
       </c>
       <c r="J43">
         <f>_xlfn.LET(
@@ -4799,7 +5803,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41389576530098682</v>
+        <v>0.35476779882941728</v>
       </c>
       <c r="K43">
         <f>_xlfn.LET(
@@ -4811,7 +5815,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40353440631589499</v>
+        <v>0.34588663398505293</v>
       </c>
       <c r="L43">
         <f>_xlfn.LET(
@@ -4823,7 +5827,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39549208051874096</v>
+        <v>0.33899321187320658</v>
       </c>
       <c r="M43">
         <f>_xlfn.LET(
@@ -4835,10 +5839,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3910462300841957</v>
+        <v>0.33518248292931063</v>
+      </c>
+      <c r="O43" s="7">
+        <v>9</v>
+      </c>
+      <c r="P43" cm="1">
+        <f t="array" ref="P43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.26623000000000002</v>
+      </c>
+      <c r="Q43" cm="1">
+        <f t="array" ref="Q43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.36811000000000005</v>
+      </c>
+      <c r="R43" cm="1">
+        <f t="array" ref="R43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.46999000000000002</v>
+      </c>
+      <c r="S43" cm="1">
+        <f t="array" ref="S43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.57187000000000021</v>
+      </c>
+      <c r="T43" cm="1">
+        <f t="array" ref="T43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.67375000000000007</v>
+      </c>
+      <c r="U43" cm="1">
+        <f t="array" ref="U43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.77563000000000004</v>
+      </c>
+      <c r="V43" cm="1">
+        <f t="array" ref="V43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.87751000000000001</v>
+      </c>
+      <c r="W43" cm="1">
+        <f t="array" ref="W43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.9793900000000002</v>
+      </c>
+      <c r="X43" cm="1">
+        <f t="array" ref="X43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y43" cm="1">
+        <f t="array" ref="Y43">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O43, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C44" s="7">
         <v>10</v>
       </c>
@@ -4852,7 +5979,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.49473919079995676</v>
+        <v>0.42406216354282023</v>
       </c>
       <c r="E44">
         <f>_xlfn.LET(
@@ -4864,7 +5991,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.47634792912499802</v>
+        <v>0.40829822496428397</v>
       </c>
       <c r="F44">
         <f>_xlfn.LET(
@@ -4876,7 +6003,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45905142095894047</v>
+        <v>0.39347264653623476</v>
       </c>
       <c r="G44">
         <f>_xlfn.LET(
@@ -4888,7 +6015,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.44292718055298752</v>
+        <v>0.37965186904541792</v>
       </c>
       <c r="H44">
         <f>_xlfn.LET(
@@ -4900,7 +6027,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42807169498586672</v>
+        <v>0.3669185957021715</v>
       </c>
       <c r="I44">
         <f>_xlfn.LET(
@@ -4912,7 +6039,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41460970940096675</v>
+        <v>0.35537975091511437</v>
       </c>
       <c r="J44">
         <f>_xlfn.LET(
@@ -4924,7 +6051,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40271150351572371</v>
+        <v>0.34518128872776327</v>
       </c>
       <c r="K44">
         <f>_xlfn.LET(
@@ -4936,7 +6063,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39263012843251144</v>
+        <v>0.33654011008500978</v>
       </c>
       <c r="L44">
         <f>_xlfn.LET(
@@ -4948,7 +6075,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3848051217881937</v>
+        <v>0.32983296153273745</v>
       </c>
       <c r="M44">
         <f>_xlfn.LET(
@@ -4960,10 +6087,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38047940680630743</v>
+        <v>0.3261252058339778</v>
+      </c>
+      <c r="O44" s="7">
+        <v>10</v>
+      </c>
+      <c r="P44" cm="1">
+        <f t="array" ref="P44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.26825142857142859</v>
+      </c>
+      <c r="Q44" cm="1">
+        <f t="array" ref="Q44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.37013142857142861</v>
+      </c>
+      <c r="R44" cm="1">
+        <f t="array" ref="R44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.47201142857142858</v>
+      </c>
+      <c r="S44" cm="1">
+        <f t="array" ref="S44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.57389142857142872</v>
+      </c>
+      <c r="T44" cm="1">
+        <f t="array" ref="T44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.67577142857142869</v>
+      </c>
+      <c r="U44" cm="1">
+        <f t="array" ref="U44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.77765142857142866</v>
+      </c>
+      <c r="V44" cm="1">
+        <f t="array" ref="V44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.87953142857142863</v>
+      </c>
+      <c r="W44" cm="1">
+        <f t="array" ref="W44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.98141142857142871</v>
+      </c>
+      <c r="X44" cm="1">
+        <f t="array" ref="X44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y44" cm="1">
+        <f t="array" ref="Y44">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O44, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C45" s="7">
         <v>11</v>
       </c>
@@ -4977,7 +6227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.48262989148151603</v>
+        <v>0.41368276412701388</v>
       </c>
       <c r="E45">
         <f>_xlfn.LET(
@@ -4989,7 +6239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.46468877666495706</v>
+        <v>0.39830466571282036</v>
       </c>
       <c r="F45">
         <f>_xlfn.LET(
@@ -5001,7 +6251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.44781562003126552</v>
+        <v>0.3838419600267991</v>
       </c>
       <c r="G45">
         <f>_xlfn.LET(
@@ -5013,7 +6263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43208603858297967</v>
+        <v>0.37035946164255401</v>
       </c>
       <c r="H45">
         <f>_xlfn.LET(
@@ -5025,7 +6275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41759415776882414</v>
+        <v>0.35793784951613494</v>
       </c>
       <c r="I45">
         <f>_xlfn.LET(
@@ -5037,7 +6287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40446166945420198</v>
+        <v>0.34668143096074466</v>
       </c>
       <c r="J45">
         <f>_xlfn.LET(
@@ -5049,7 +6299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39285468556854203</v>
+        <v>0.33673258763017894</v>
       </c>
       <c r="K45">
         <f>_xlfn.LET(
@@ -5061,7 +6311,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38302006350327161</v>
+        <v>0.32830291157423286</v>
       </c>
       <c r="L45">
         <f>_xlfn.LET(
@@ -5073,7 +6323,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37538658271618719</v>
+        <v>0.32175992804244624</v>
       </c>
       <c r="M45">
         <f>_xlfn.LET(
@@ -5085,10 +6335,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37116674448402276</v>
+        <v>0.31814292384344817</v>
+      </c>
+      <c r="O45" s="7">
+        <v>11</v>
+      </c>
+      <c r="P45" cm="1">
+        <f t="array" ref="P45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.27027285714285715</v>
+      </c>
+      <c r="Q45" cm="1">
+        <f t="array" ref="Q45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.37215285714285717</v>
+      </c>
+      <c r="R45" cm="1">
+        <f t="array" ref="R45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.47403285714285714</v>
+      </c>
+      <c r="S45" cm="1">
+        <f t="array" ref="S45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.57591285714285734</v>
+      </c>
+      <c r="T45" cm="1">
+        <f t="array" ref="T45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.67779285714285731</v>
+      </c>
+      <c r="U45" cm="1">
+        <f t="array" ref="U45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.77967285714285728</v>
+      </c>
+      <c r="V45" cm="1">
+        <f t="array" ref="V45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.88155285714285725</v>
+      </c>
+      <c r="W45" cm="1">
+        <f t="array" ref="W45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.98343285714285744</v>
+      </c>
+      <c r="X45" cm="1">
+        <f t="array" ref="X45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y45" cm="1">
+        <f t="array" ref="Y45">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O45, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C46" s="7">
         <v>12</v>
       </c>
@@ -5102,7 +6475,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.47183395416813867</v>
+        <v>0.40442910357269035</v>
       </c>
       <c r="E46">
         <f>_xlfn.LET(
@@ -5114,7 +6487,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45429416375006887</v>
+        <v>0.38939499750005907</v>
       </c>
       <c r="F46">
         <f>_xlfn.LET(
@@ -5126,7 +6499,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43779844238201521</v>
+        <v>0.37525580775601303</v>
       </c>
       <c r="G46">
         <f>_xlfn.LET(
@@ -5138,7 +6511,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42242071559146732</v>
+        <v>0.36207489907840062</v>
       </c>
       <c r="H46">
         <f>_xlfn.LET(
@@ -5150,7 +6523,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40825300333707976</v>
+        <v>0.34993114571749695</v>
       </c>
       <c r="I46">
         <f>_xlfn.LET(
@@ -5162,7 +6535,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39541427536162388</v>
+        <v>0.33892652173853477</v>
       </c>
       <c r="J46">
         <f>_xlfn.LET(
@@ -5174,7 +6547,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38406692784047147</v>
+        <v>0.32920022386326131</v>
       </c>
       <c r="K46">
         <f>_xlfn.LET(
@@ -5186,7 +6559,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37445229621754916</v>
+        <v>0.32095911104361358</v>
       </c>
       <c r="L46">
         <f>_xlfn.LET(
@@ -5198,7 +6571,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36698956859249382</v>
+        <v>0.31456248736499476</v>
       </c>
       <c r="M46">
         <f>_xlfn.LET(
@@ -5210,10 +6583,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36286412382793498</v>
+        <v>0.31102639185251574</v>
+      </c>
+      <c r="O46" s="7">
+        <v>12</v>
+      </c>
+      <c r="P46" cm="1">
+        <f t="array" ref="P46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.27229428571428571</v>
+      </c>
+      <c r="Q46" cm="1">
+        <f t="array" ref="Q46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.37417428571428574</v>
+      </c>
+      <c r="R46" cm="1">
+        <f t="array" ref="R46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.47605428571428571</v>
+      </c>
+      <c r="S46" cm="1">
+        <f t="array" ref="S46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.57793428571428584</v>
+      </c>
+      <c r="T46" cm="1">
+        <f t="array" ref="T46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.67981428571428593</v>
+      </c>
+      <c r="U46" cm="1">
+        <f t="array" ref="U46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.7816942857142859</v>
+      </c>
+      <c r="V46" cm="1">
+        <f t="array" ref="V46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.88357428571428587</v>
+      </c>
+      <c r="W46" cm="1">
+        <f t="array" ref="W46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.98545428571428595</v>
+      </c>
+      <c r="X46" cm="1">
+        <f t="array" ref="X46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y46" cm="1">
+        <f t="array" ref="Y46">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O46, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C47" s="7">
         <v>13</v>
       </c>
@@ -5227,7 +6723,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.46211603967890125</v>
+        <v>0.39609946258191536</v>
       </c>
       <c r="E47">
         <f>_xlfn.LET(
@@ -5239,7 +6735,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.4449374996158264</v>
+        <v>0.38137499967070843</v>
       </c>
       <c r="F47">
         <f>_xlfn.LET(
@@ -5251,7 +6747,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42878152490711541</v>
+        <v>0.3675270213489561</v>
       </c>
       <c r="G47">
         <f>_xlfn.LET(
@@ -5263,7 +6759,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.4137205185065887</v>
+        <v>0.35461758729136184</v>
       </c>
       <c r="H47">
         <f>_xlfn.LET(
@@ -5275,7 +6771,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3998446051254701</v>
+        <v>0.342723947250403</v>
       </c>
       <c r="I47">
         <f>_xlfn.LET(
@@ -5287,7 +6783,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3872703042000683</v>
+        <v>0.33194597502862999</v>
       </c>
       <c r="J47">
         <f>_xlfn.LET(
@@ -5299,7 +6795,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37615666718642832</v>
+        <v>0.32242000044551</v>
       </c>
       <c r="K47">
         <f>_xlfn.LET(
@@ -5311,7 +6807,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36674005897223211</v>
+        <v>0.31434862197619901</v>
       </c>
       <c r="L47">
         <f>_xlfn.LET(
@@ -5323,7 +6819,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.359431034039143</v>
+        <v>0.30808374346212269</v>
       </c>
       <c r="M47">
         <f>_xlfn.LET(
@@ -5335,10 +6831,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35539055713053835</v>
+        <v>0.30462047754046151</v>
+      </c>
+      <c r="O47" s="7">
+        <v>13</v>
+      </c>
+      <c r="P47" cm="1">
+        <f t="array" ref="P47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.27431571428571427</v>
+      </c>
+      <c r="Q47" cm="1">
+        <f t="array" ref="Q47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.3761957142857143</v>
+      </c>
+      <c r="R47" cm="1">
+        <f t="array" ref="R47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.47807571428571427</v>
+      </c>
+      <c r="S47" cm="1">
+        <f t="array" ref="S47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.57995571428571446</v>
+      </c>
+      <c r="T47" cm="1">
+        <f t="array" ref="T47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.68183571428571443</v>
+      </c>
+      <c r="U47" cm="1">
+        <f t="array" ref="U47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.7837157142857144</v>
+      </c>
+      <c r="V47" cm="1">
+        <f t="array" ref="V47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.88559571428571449</v>
+      </c>
+      <c r="W47" cm="1">
+        <f t="array" ref="W47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.98747571428571457</v>
+      </c>
+      <c r="X47" cm="1">
+        <f t="array" ref="X47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y47" cm="1">
+        <f t="array" ref="Y47">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O47, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C48" s="7">
         <v>14</v>
       </c>
@@ -5352,7 +6971,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.45329718817689096</v>
+        <v>0.38854044700876378</v>
       </c>
       <c r="E48">
         <f>_xlfn.LET(
@@ -5364,7 +6983,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43644647701571454</v>
+        <v>0.37409698029918392</v>
       </c>
       <c r="F48">
         <f>_xlfn.LET(
@@ -5376,7 +6995,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42059881695006457</v>
+        <v>0.36051327167148389</v>
       </c>
       <c r="G48">
         <f>_xlfn.LET(
@@ -5388,7 +7007,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.4058252292225823</v>
+        <v>0.34785019647649917</v>
       </c>
       <c r="H48">
         <f>_xlfn.LET(
@@ -5400,7 +7019,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39221411863785194</v>
+        <v>0.33618353026101594</v>
       </c>
       <c r="I48">
         <f>_xlfn.LET(
@@ -5412,7 +7031,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37987978101837605</v>
+        <v>0.32561124087289378</v>
       </c>
       <c r="J48">
         <f>_xlfn.LET(
@@ -5424,7 +7043,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36897823254106693</v>
+        <v>0.31626705646377168</v>
       </c>
       <c r="K48">
         <f>_xlfn.LET(
@@ -5436,7 +7055,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35974132739355347</v>
+        <v>0.30834970919447446</v>
       </c>
       <c r="L48">
         <f>_xlfn.LET(
@@ -5448,7 +7067,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35257178518769072</v>
+        <v>0.30220438730373494</v>
       </c>
       <c r="M48">
         <f>_xlfn.LET(
@@ -5460,10 +7079,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34860841524529101</v>
+        <v>0.29880721306739227</v>
+      </c>
+      <c r="O48" s="7">
+        <v>14</v>
+      </c>
+      <c r="P48" cm="1">
+        <f t="array" ref="P48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.27633714285714289</v>
+      </c>
+      <c r="Q48" cm="1">
+        <f t="array" ref="Q48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.37821714285714286</v>
+      </c>
+      <c r="R48" cm="1">
+        <f t="array" ref="R48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.48009714285714283</v>
+      </c>
+      <c r="S48" cm="1">
+        <f t="array" ref="S48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.58197714285714297</v>
+      </c>
+      <c r="T48" cm="1">
+        <f t="array" ref="T48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.68385714285714305</v>
+      </c>
+      <c r="U48" cm="1">
+        <f t="array" ref="U48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.78573714285714302</v>
+      </c>
+      <c r="V48" cm="1">
+        <f t="array" ref="V48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.88761714285714299</v>
+      </c>
+      <c r="W48" cm="1">
+        <f t="array" ref="W48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.98949714285714307</v>
+      </c>
+      <c r="X48" cm="1">
+        <f t="array" ref="X48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y48" cm="1">
+        <f t="array" ref="Y48">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O48, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C49" s="7">
         <v>15</v>
       </c>
@@ -5477,7 +7219,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.44523837296638263</v>
+        <v>0.38163289111404225</v>
       </c>
       <c r="E49">
         <f>_xlfn.LET(
@@ -5489,7 +7231,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42868723738377912</v>
+        <v>0.36744620347181062</v>
       </c>
       <c r="F49">
         <f>_xlfn.LET(
@@ -5501,7 +7243,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41312132043791694</v>
+        <v>0.35410398894678602</v>
       </c>
       <c r="G49">
         <f>_xlfn.LET(
@@ -5513,7 +7255,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39861038074046307</v>
+        <v>0.3416660406346827</v>
       </c>
       <c r="H49">
         <f>_xlfn.LET(
@@ -5525,7 +7267,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38524125141631205</v>
+        <v>0.33020678692826749</v>
       </c>
       <c r="I49">
         <f>_xlfn.LET(
@@ -5537,7 +7279,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37312619631217475</v>
+        <v>0.31982245398186415</v>
       </c>
       <c r="J49">
         <f>_xlfn.LET(
@@ -5549,7 +7291,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36241845791570987</v>
+        <v>0.31064439249917991</v>
       </c>
       <c r="K49">
         <f>_xlfn.LET(
@@ -5561,7 +7303,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35334576846077598</v>
+        <v>0.30286780153780801</v>
       </c>
       <c r="L49">
         <f>_xlfn.LET(
@@ -5573,7 +7315,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34630368792308142</v>
+        <v>0.29683173250549844</v>
       </c>
       <c r="M49">
         <f>_xlfn.LET(
@@ -5585,10 +7327,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34241077962661676</v>
+        <v>0.29349495396567155</v>
+      </c>
+      <c r="O49" s="7">
+        <v>15</v>
+      </c>
+      <c r="P49" cm="1">
+        <f t="array" ref="P49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.27835857142857146</v>
+      </c>
+      <c r="Q49" cm="1">
+        <f t="array" ref="Q49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.38023857142857148</v>
+      </c>
+      <c r="R49" cm="1">
+        <f t="array" ref="R49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.48211857142857145</v>
+      </c>
+      <c r="S49" cm="1">
+        <f t="array" ref="S49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.58399857142857159</v>
+      </c>
+      <c r="T49" cm="1">
+        <f t="array" ref="T49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.68587857142857156</v>
+      </c>
+      <c r="U49" cm="1">
+        <f t="array" ref="U49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.78775857142857164</v>
+      </c>
+      <c r="V49" cm="1">
+        <f t="array" ref="V49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.88963857142857161</v>
+      </c>
+      <c r="W49" cm="1">
+        <f t="array" ref="W49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.99151857142857169</v>
+      </c>
+      <c r="X49" cm="1">
+        <f t="array" ref="X49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y49" cm="1">
+        <f t="array" ref="Y49">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O49, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C50" s="7">
         <v>16</v>
       </c>
@@ -5602,7 +7467,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43782959967323654</v>
+        <v>0.37528251400563128</v>
       </c>
       <c r="E50">
         <f>_xlfn.LET(
@@ -5614,7 +7479,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42155387523828103</v>
+        <v>0.3613318930613838</v>
       </c>
       <c r="F50">
         <f>_xlfn.LET(
@@ -5626,7 +7491,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40624697538697774</v>
+        <v>0.34821169318883805</v>
       </c>
       <c r="G50">
         <f>_xlfn.LET(
@@ -5638,7 +7503,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39197749794663495</v>
+        <v>0.33598071252568712</v>
       </c>
       <c r="H50">
         <f>_xlfn.LET(
@@ -5650,7 +7515,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37883083113762944</v>
+        <v>0.32471214097511097</v>
       </c>
       <c r="I50">
         <f>_xlfn.LET(
@@ -5662,7 +7527,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36691737073455644</v>
+        <v>0.31450060348676273</v>
       </c>
       <c r="J50">
         <f>_xlfn.LET(
@@ -5674,7 +7539,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3563878092677511</v>
+        <v>0.3054752650866438</v>
       </c>
       <c r="K50">
         <f>_xlfn.LET(
@@ -5686,7 +7551,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34746608950323915</v>
+        <v>0.29782807671706218</v>
       </c>
       <c r="L50">
         <f>_xlfn.LET(
@@ -5698,7 +7563,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34054118929272137</v>
+        <v>0.29189244796518976</v>
       </c>
       <c r="M50">
         <f>_xlfn.LET(
@@ -5710,10 +7575,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33671305904947652</v>
+        <v>0.28861119347097991</v>
+      </c>
+      <c r="O50" s="7">
+        <v>16</v>
+      </c>
+      <c r="P50" cm="1">
+        <f t="array" ref="P50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.28038000000000002</v>
+      </c>
+      <c r="Q50" cm="1">
+        <f t="array" ref="Q50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.38226000000000004</v>
+      </c>
+      <c r="R50" cm="1">
+        <f t="array" ref="R50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.48414000000000007</v>
+      </c>
+      <c r="S50" cm="1">
+        <f t="array" ref="S50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.58602000000000021</v>
+      </c>
+      <c r="T50" cm="1">
+        <f t="array" ref="T50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.68790000000000018</v>
+      </c>
+      <c r="U50" cm="1">
+        <f t="array" ref="U50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.78978000000000015</v>
+      </c>
+      <c r="V50" cm="1">
+        <f t="array" ref="V50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.89166000000000012</v>
+      </c>
+      <c r="W50" cm="1">
+        <f t="array" ref="W50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.9935400000000002</v>
+      </c>
+      <c r="X50" cm="1">
+        <f t="array" ref="X50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y50" cm="1">
+        <f t="array" ref="Y50">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O50, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C51" s="7">
         <v>17</v>
       </c>
@@ -5727,7 +7715,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.43098245911471034</v>
+        <v>0.36941353638403751</v>
       </c>
       <c r="E51">
         <f>_xlfn.LET(
@@ -5739,7 +7727,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41496126788852195</v>
+        <v>0.35568108676159027</v>
       </c>
       <c r="F51">
         <f>_xlfn.LET(
@@ -5751,7 +7739,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39989374996771243</v>
+        <v>0.34276607140089638</v>
       </c>
       <c r="G51">
         <f>_xlfn.LET(
@@ -5763,7 +7751,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.385847430390163</v>
+        <v>0.33072636890585405</v>
       </c>
       <c r="H51">
         <f>_xlfn.LET(
@@ -5775,7 +7763,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37290636200480121</v>
+        <v>0.31963402457554385</v>
       </c>
       <c r="I51">
         <f>_xlfn.LET(
@@ -5787,7 +7775,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36117921412600512</v>
+        <v>0.30958218353657591</v>
       </c>
       <c r="J51">
         <f>_xlfn.LET(
@@ -5799,7 +7787,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35081432262997536</v>
+        <v>0.30069799082569321</v>
       </c>
       <c r="K51">
         <f>_xlfn.LET(
@@ -5811,7 +7799,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34203212808097416</v>
+        <v>0.29317039549797785</v>
       </c>
       <c r="L51">
         <f>_xlfn.LET(
@@ -5823,7 +7811,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33521552517408904</v>
+        <v>0.28732759300636207</v>
       </c>
       <c r="M51">
         <f>_xlfn.LET(
@@ -5835,10 +7823,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3314472623904024</v>
+        <v>0.28409765347748783</v>
+      </c>
+      <c r="O51" s="7">
+        <v>17</v>
+      </c>
+      <c r="P51" cm="1">
+        <f t="array" ref="P51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.28240142857142858</v>
+      </c>
+      <c r="Q51" cm="1">
+        <f t="array" ref="Q51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.38428142857142861</v>
+      </c>
+      <c r="R51" cm="1">
+        <f t="array" ref="R51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.48616142857142863</v>
+      </c>
+      <c r="S51" cm="1">
+        <f t="array" ref="S51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.58804142857142871</v>
+      </c>
+      <c r="T51" cm="1">
+        <f t="array" ref="T51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.68992142857142869</v>
+      </c>
+      <c r="U51" cm="1">
+        <f t="array" ref="U51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.79180142857142877</v>
+      </c>
+      <c r="V51" cm="1">
+        <f t="array" ref="V51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.89368142857142874</v>
+      </c>
+      <c r="W51" cm="1">
+        <f t="array" ref="W51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.99556142857142882</v>
+      </c>
+      <c r="X51" cm="1">
+        <f t="array" ref="X51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y51" cm="1">
+        <f t="array" ref="Y51">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O51, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C52" s="7">
         <v>18</v>
       </c>
@@ -5852,7 +7963,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.42462490534545133</v>
+        <v>0.36396420458181544</v>
       </c>
       <c r="E52">
         <f>_xlfn.LET(
@@ -5864,7 +7975,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40884004759992765</v>
+        <v>0.35043432651422374</v>
       </c>
       <c r="F52">
         <f>_xlfn.LET(
@@ -5876,7 +7987,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39399479523384073</v>
+        <v>0.33770982448614928</v>
       </c>
       <c r="G52">
         <f>_xlfn.LET(
@@ -5888,7 +7999,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38015567720263249</v>
+        <v>0.32584772331654216</v>
       </c>
       <c r="H52">
         <f>_xlfn.LET(
@@ -5900,7 +8011,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.367405506466007</v>
+        <v>0.31491900554229169</v>
       </c>
       <c r="I52">
         <f>_xlfn.LET(
@@ -5912,7 +8023,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35585134932412549</v>
+        <v>0.30501544227782196</v>
       </c>
       <c r="J52">
         <f>_xlfn.LET(
@@ -5924,7 +8035,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34563935350541375</v>
+        <v>0.2962623030046404</v>
       </c>
       <c r="K52">
         <f>_xlfn.LET(
@@ -5936,7 +8047,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33698670778810297</v>
+        <v>0.28884574953265968</v>
       </c>
       <c r="L52">
         <f>_xlfn.LET(
@@ -5948,7 +8059,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33027065867079253</v>
+        <v>0.28308913600353652</v>
       </c>
       <c r="M52">
         <f>_xlfn.LET(
@@ -5960,10 +8071,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32655798268131836</v>
+        <v>0.2799068422982729</v>
+      </c>
+      <c r="O52" s="7">
+        <v>18</v>
+      </c>
+      <c r="P52" cm="1">
+        <f t="array" ref="P52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.2844228571428572</v>
+      </c>
+      <c r="Q52" cm="1">
+        <f t="array" ref="Q52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.38630285714285717</v>
+      </c>
+      <c r="R52" cm="1">
+        <f t="array" ref="R52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.4881828571428572</v>
+      </c>
+      <c r="S52" cm="1">
+        <f t="array" ref="S52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.59006285714285733</v>
+      </c>
+      <c r="T52" cm="1">
+        <f t="array" ref="T52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.6919428571428573</v>
+      </c>
+      <c r="U52" cm="1">
+        <f t="array" ref="U52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.79382285714285727</v>
+      </c>
+      <c r="V52" cm="1">
+        <f t="array" ref="V52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.89570285714285724</v>
+      </c>
+      <c r="W52" cm="1">
+        <f t="array" ref="W52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.99758285714285733</v>
+      </c>
+      <c r="X52" cm="1">
+        <f t="array" ref="X52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y52" cm="1">
+        <f t="array" ref="Y52">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O52, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C53" s="7">
         <v>19</v>
       </c>
@@ -5977,7 +8211,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41869751000356209</v>
+        <v>0.35888358000305332</v>
       </c>
       <c r="E53">
         <f>_xlfn.LET(
@@ -5989,7 +8223,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40313299517974505</v>
+        <v>0.3455425672969244</v>
       </c>
       <c r="F53">
         <f>_xlfn.LET(
@@ -6001,7 +8235,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38849496965931934</v>
+        <v>0.33299568827941656</v>
       </c>
       <c r="G53">
         <f>_xlfn.LET(
@@ -6013,7 +8247,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37484903371121875</v>
+        <v>0.32129917175247324</v>
       </c>
       <c r="H53">
         <f>_xlfn.LET(
@@ -6025,7 +8259,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36227684429806523</v>
+        <v>0.31052300939834171</v>
       </c>
       <c r="I53">
         <f>_xlfn.LET(
@@ -6037,7 +8271,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35088397316734349</v>
+        <v>0.30075769128629443</v>
       </c>
       <c r="J53">
         <f>_xlfn.LET(
@@ -6049,7 +8283,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34081452795196476</v>
+        <v>0.29212673824454122</v>
       </c>
       <c r="K53">
         <f>_xlfn.LET(
@@ -6061,7 +8295,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33228266566321446</v>
+        <v>0.28481371342561246</v>
       </c>
       <c r="L53">
         <f>_xlfn.LET(
@@ -6073,7 +8307,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32566036676581039</v>
+        <v>0.2791374572278375</v>
       </c>
       <c r="M53">
         <f>_xlfn.LET(
@@ -6085,10 +8319,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32199951651262476</v>
+        <v>0.2759995855822498</v>
+      </c>
+      <c r="O53" s="7">
+        <v>19</v>
+      </c>
+      <c r="P53" cm="1">
+        <f t="array" ref="P53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.28644428571428576</v>
+      </c>
+      <c r="Q53" cm="1">
+        <f t="array" ref="Q53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.38832428571428579</v>
+      </c>
+      <c r="R53" cm="1">
+        <f t="array" ref="R53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.49020428571428576</v>
+      </c>
+      <c r="S53" cm="1">
+        <f t="array" ref="S53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.59208428571428584</v>
+      </c>
+      <c r="T53" cm="1">
+        <f t="array" ref="T53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.69396428571428592</v>
+      </c>
+      <c r="U53" cm="1">
+        <f t="array" ref="U53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.79584428571428589</v>
+      </c>
+      <c r="V53" cm="1">
+        <f t="array" ref="V53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.89772428571428586</v>
+      </c>
+      <c r="W53" cm="1">
+        <f t="array" ref="W53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.99960428571428595</v>
+      </c>
+      <c r="X53" cm="1">
+        <f t="array" ref="X53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y53" cm="1">
+        <f t="array" ref="Y53">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O53, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C54" s="7">
         <v>20</v>
       </c>
@@ -6102,7 +8459,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.41315072150481091</v>
+        <v>0.35412918986126657</v>
       </c>
       <c r="E54">
         <f>_xlfn.LET(
@@ -6114,7 +8471,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39779240105700686</v>
+        <v>0.34096491519172017</v>
       </c>
       <c r="F54">
         <f>_xlfn.LET(
@@ -6126,7 +8483,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38334829603923815</v>
+        <v>0.32858425374791844</v>
       </c>
       <c r="G54">
         <f>_xlfn.LET(
@@ -6138,7 +8495,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36988313766626807</v>
+        <v>0.31704268942822972</v>
       </c>
       <c r="H54">
         <f>_xlfn.LET(
@@ -6150,7 +8507,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.357477501131923</v>
+        <v>0.30640928668450546</v>
       </c>
       <c r="I54">
         <f>_xlfn.LET(
@@ -6162,7 +8519,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34623555959845415</v>
+        <v>0.29677333679867496</v>
       </c>
       <c r="J54">
         <f>_xlfn.LET(
@@ -6174,7 +8531,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33629951160081617</v>
+        <v>0.28825672422927101</v>
       </c>
       <c r="K54">
         <f>_xlfn.LET(
@@ -6186,7 +8543,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32788067705759932</v>
+        <v>0.28104058033508517</v>
       </c>
       <c r="L54">
         <f>_xlfn.LET(
@@ -6198,7 +8555,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32134610853948292</v>
+        <v>0.27543952160527113</v>
       </c>
       <c r="M54">
         <f>_xlfn.LET(
@@ -6210,10 +8567,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31773375621521938</v>
+        <v>0.2723432196130452</v>
+      </c>
+      <c r="O54" s="7">
+        <v>20</v>
+      </c>
+      <c r="P54" cm="1">
+        <f t="array" ref="P54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.28846571428571427</v>
+      </c>
+      <c r="Q54" cm="1">
+        <f t="array" ref="Q54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.39034571428571435</v>
+      </c>
+      <c r="R54" cm="1">
+        <f t="array" ref="R54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.49222571428571432</v>
+      </c>
+      <c r="S54" cm="1">
+        <f t="array" ref="S54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.59410571428571446</v>
+      </c>
+      <c r="T54" cm="1">
+        <f t="array" ref="T54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.69598571428571443</v>
+      </c>
+      <c r="U54" cm="1">
+        <f t="array" ref="U54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.7978657142857144</v>
+      </c>
+      <c r="V54" cm="1">
+        <f t="array" ref="V54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.89974571428571437</v>
+      </c>
+      <c r="W54" cm="1">
+        <f t="array" ref="W54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X54" cm="1">
+        <f t="array" ref="X54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y54" cm="1">
+        <f t="array" ref="Y54">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O54, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C55" s="7">
         <v>21</v>
       </c>
@@ -6227,7 +8707,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40794282378919366</v>
+        <v>0.34966527753359461</v>
       </c>
       <c r="E55">
         <f>_xlfn.LET(
@@ -6239,7 +8719,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.39277809990993617</v>
+        <v>0.3366669427799453</v>
       </c>
       <c r="F55">
         <f>_xlfn.LET(
@@ -6251,7 +8731,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3785160674812027</v>
+        <v>0.32444234355531665</v>
       </c>
       <c r="G55">
         <f>_xlfn.LET(
@@ -6263,7 +8743,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36522064175997665</v>
+        <v>0.31304626436569438</v>
       </c>
       <c r="H55">
         <f>_xlfn.LET(
@@ -6275,7 +8755,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.35297138226385311</v>
+        <v>0.30254689908330268</v>
       </c>
       <c r="I55">
         <f>_xlfn.LET(
@@ -6287,7 +8767,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34187114901887045</v>
+        <v>0.29303241344474606</v>
       </c>
       <c r="J55">
         <f>_xlfn.LET(
@@ -6299,7 +8779,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33206034810171847</v>
+        <v>0.28462315551575867</v>
       </c>
       <c r="K55">
         <f>_xlfn.LET(
@@ -6311,7 +8791,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32374763567545228</v>
+        <v>0.277497973436102</v>
       </c>
       <c r="L55">
         <f>_xlfn.LET(
@@ -6323,7 +8803,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31729543749505207</v>
+        <v>0.2719675178529018</v>
       </c>
       <c r="M55">
         <f>_xlfn.LET(
@@ -6335,10 +8815,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31372862003358387</v>
+        <v>0.26891024574307193</v>
+      </c>
+      <c r="O55" s="7">
+        <v>21</v>
+      </c>
+      <c r="P55" cm="1">
+        <f t="array" ref="P55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.29048714285714283</v>
+      </c>
+      <c r="Q55" cm="1">
+        <f t="array" ref="Q55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.39236714285714291</v>
+      </c>
+      <c r="R55" cm="1">
+        <f t="array" ref="R55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.49424714285714288</v>
+      </c>
+      <c r="S55" cm="1">
+        <f t="array" ref="S55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.59612714285714308</v>
+      </c>
+      <c r="T55" cm="1">
+        <f t="array" ref="T55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.69800714285714305</v>
+      </c>
+      <c r="U55" cm="1">
+        <f t="array" ref="U55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.79988714285714302</v>
+      </c>
+      <c r="V55" cm="1">
+        <f t="array" ref="V55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.90176714285714299</v>
+      </c>
+      <c r="W55" cm="1">
+        <f t="array" ref="W55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X55" cm="1">
+        <f t="array" ref="X55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y55" cm="1">
+        <f t="array" ref="Y55">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O55, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C56" s="7">
         <v>22</v>
       </c>
@@ -6352,7 +8955,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E56">
         <f>_xlfn.LET(
@@ -6364,7 +8967,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F56">
         <f>_xlfn.LET(
@@ -6376,7 +8979,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G56">
         <f>_xlfn.LET(
@@ -6388,7 +8991,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H56">
         <f>_xlfn.LET(
@@ -6400,7 +9003,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I56">
         <f>_xlfn.LET(
@@ -6412,7 +9015,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J56">
         <f>_xlfn.LET(
@@ -6424,7 +9027,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K56">
         <f>_xlfn.LET(
@@ -6436,7 +9039,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L56">
         <f>_xlfn.LET(
@@ -6448,7 +9051,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M56">
         <f>_xlfn.LET(
@@ -6460,10 +9063,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O56" s="7">
+        <v>22</v>
+      </c>
+      <c r="P56" cm="1">
+        <f t="array" ref="P56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.29250857142857145</v>
+      </c>
+      <c r="Q56" cm="1">
+        <f t="array" ref="Q56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.39438857142857148</v>
+      </c>
+      <c r="R56" cm="1">
+        <f t="array" ref="R56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.49626857142857145</v>
+      </c>
+      <c r="S56" cm="1">
+        <f t="array" ref="S56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.59814857142857158</v>
+      </c>
+      <c r="T56" cm="1">
+        <f t="array" ref="T56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.70002857142857156</v>
+      </c>
+      <c r="U56" cm="1">
+        <f t="array" ref="U56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.80190857142857153</v>
+      </c>
+      <c r="V56" cm="1">
+        <f t="array" ref="V56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.9037885714285715</v>
+      </c>
+      <c r="W56" cm="1">
+        <f t="array" ref="W56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X56" cm="1">
+        <f t="array" ref="X56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y56" cm="1">
+        <f t="array" ref="Y56">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O56, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C57" s="7">
         <v>23</v>
       </c>
@@ -6477,7 +9203,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E57">
         <f>_xlfn.LET(
@@ -6489,7 +9215,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F57">
         <f>_xlfn.LET(
@@ -6501,7 +9227,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G57">
         <f>_xlfn.LET(
@@ -6513,7 +9239,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H57">
         <f>_xlfn.LET(
@@ -6525,7 +9251,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I57">
         <f>_xlfn.LET(
@@ -6537,7 +9263,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J57">
         <f>_xlfn.LET(
@@ -6549,7 +9275,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K57">
         <f>_xlfn.LET(
@@ -6561,7 +9287,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L57">
         <f>_xlfn.LET(
@@ -6573,7 +9299,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M57">
         <f>_xlfn.LET(
@@ -6585,10 +9311,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O57" s="7">
+        <v>23</v>
+      </c>
+      <c r="P57" cm="1">
+        <f t="array" ref="P57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.29453000000000001</v>
+      </c>
+      <c r="Q57" cm="1">
+        <f t="array" ref="Q57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.39641000000000004</v>
+      </c>
+      <c r="R57" cm="1">
+        <f t="array" ref="R57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.49829000000000001</v>
+      </c>
+      <c r="S57" cm="1">
+        <f t="array" ref="S57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.6001700000000002</v>
+      </c>
+      <c r="T57" cm="1">
+        <f t="array" ref="T57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.70205000000000017</v>
+      </c>
+      <c r="U57" cm="1">
+        <f t="array" ref="U57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.80393000000000014</v>
+      </c>
+      <c r="V57" cm="1">
+        <f t="array" ref="V57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.90581000000000012</v>
+      </c>
+      <c r="W57" cm="1">
+        <f t="array" ref="W57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X57" cm="1">
+        <f t="array" ref="X57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y57" cm="1">
+        <f t="array" ref="Y57">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O57, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C58" s="7">
         <v>24</v>
       </c>
@@ -6602,7 +9451,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E58">
         <f>_xlfn.LET(
@@ -6614,7 +9463,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F58">
         <f>_xlfn.LET(
@@ -6626,7 +9475,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G58">
         <f>_xlfn.LET(
@@ -6638,7 +9487,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H58">
         <f>_xlfn.LET(
@@ -6650,7 +9499,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I58">
         <f>_xlfn.LET(
@@ -6662,7 +9511,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J58">
         <f>_xlfn.LET(
@@ -6674,7 +9523,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K58">
         <f>_xlfn.LET(
@@ -6686,7 +9535,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L58">
         <f>_xlfn.LET(
@@ -6698,7 +9547,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M58">
         <f>_xlfn.LET(
@@ -6710,10 +9559,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O58" s="7">
+        <v>24</v>
+      </c>
+      <c r="P58" cm="1">
+        <f t="array" ref="P58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.29655142857142858</v>
+      </c>
+      <c r="Q58" cm="1">
+        <f t="array" ref="Q58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.3984314285714286</v>
+      </c>
+      <c r="R58" cm="1">
+        <f t="array" ref="R58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.50031142857142863</v>
+      </c>
+      <c r="S58" cm="1">
+        <f t="array" ref="S58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.60219142857142871</v>
+      </c>
+      <c r="T58" cm="1">
+        <f t="array" ref="T58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.70407142857142868</v>
+      </c>
+      <c r="U58" cm="1">
+        <f t="array" ref="U58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.80595142857142865</v>
+      </c>
+      <c r="V58" cm="1">
+        <f t="array" ref="V58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.90783142857142862</v>
+      </c>
+      <c r="W58" cm="1">
+        <f t="array" ref="W58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X58" cm="1">
+        <f t="array" ref="X58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y58" cm="1">
+        <f t="array" ref="Y58">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O58, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C59" s="7">
         <v>25</v>
       </c>
@@ -6727,7 +9699,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E59">
         <f>_xlfn.LET(
@@ -6739,7 +9711,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F59">
         <f>_xlfn.LET(
@@ -6751,7 +9723,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G59">
         <f>_xlfn.LET(
@@ -6763,7 +9735,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H59">
         <f>_xlfn.LET(
@@ -6775,7 +9747,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I59">
         <f>_xlfn.LET(
@@ -6787,7 +9759,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J59">
         <f>_xlfn.LET(
@@ -6799,7 +9771,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K59">
         <f>_xlfn.LET(
@@ -6811,7 +9783,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L59">
         <f>_xlfn.LET(
@@ -6823,7 +9795,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M59">
         <f>_xlfn.LET(
@@ -6835,10 +9807,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O59" s="7">
+        <v>25</v>
+      </c>
+      <c r="P59" cm="1">
+        <f t="array" ref="P59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.29857285714285714</v>
+      </c>
+      <c r="Q59" cm="1">
+        <f t="array" ref="Q59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.40045285714285722</v>
+      </c>
+      <c r="R59" cm="1">
+        <f t="array" ref="R59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.50233285714285725</v>
+      </c>
+      <c r="S59" cm="1">
+        <f t="array" ref="S59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.60421285714285733</v>
+      </c>
+      <c r="T59" cm="1">
+        <f t="array" ref="T59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.7060928571428573</v>
+      </c>
+      <c r="U59" cm="1">
+        <f t="array" ref="U59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.80797285714285727</v>
+      </c>
+      <c r="V59" cm="1">
+        <f t="array" ref="V59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.90985285714285724</v>
+      </c>
+      <c r="W59" cm="1">
+        <f t="array" ref="W59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X59" cm="1">
+        <f t="array" ref="X59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y59" cm="1">
+        <f t="array" ref="Y59">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O59, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C60" s="7">
         <v>26</v>
       </c>
@@ -6852,7 +9947,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E60">
         <f>_xlfn.LET(
@@ -6864,7 +9959,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F60">
         <f>_xlfn.LET(
@@ -6876,7 +9971,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G60">
         <f>_xlfn.LET(
@@ -6888,7 +9983,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H60">
         <f>_xlfn.LET(
@@ -6900,7 +9995,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I60">
         <f>_xlfn.LET(
@@ -6912,7 +10007,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J60">
         <f>_xlfn.LET(
@@ -6924,7 +10019,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K60">
         <f>_xlfn.LET(
@@ -6936,7 +10031,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L60">
         <f>_xlfn.LET(
@@ -6948,7 +10043,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M60">
         <f>_xlfn.LET(
@@ -6960,10 +10055,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O60" s="7">
+        <v>26</v>
+      </c>
+      <c r="P60" cm="1">
+        <f t="array" ref="P60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.30059428571428576</v>
+      </c>
+      <c r="Q60" cm="1">
+        <f t="array" ref="Q60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.40247428571428578</v>
+      </c>
+      <c r="R60" cm="1">
+        <f t="array" ref="R60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.50435428571428575</v>
+      </c>
+      <c r="S60" cm="1">
+        <f t="array" ref="S60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.60623428571428584</v>
+      </c>
+      <c r="T60" cm="1">
+        <f t="array" ref="T60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.70811428571428581</v>
+      </c>
+      <c r="U60" cm="1">
+        <f t="array" ref="U60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.80999428571428578</v>
+      </c>
+      <c r="V60" cm="1">
+        <f t="array" ref="V60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.91187428571428575</v>
+      </c>
+      <c r="W60" cm="1">
+        <f t="array" ref="W60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X60" cm="1">
+        <f t="array" ref="X60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y60" cm="1">
+        <f t="array" ref="Y60">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O60, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C61" s="7">
         <v>27</v>
       </c>
@@ -6977,7 +10195,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E61">
         <f>_xlfn.LET(
@@ -6989,7 +10207,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F61">
         <f>_xlfn.LET(
@@ -7001,7 +10219,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G61">
         <f>_xlfn.LET(
@@ -7013,7 +10231,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H61">
         <f>_xlfn.LET(
@@ -7025,7 +10243,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I61">
         <f>_xlfn.LET(
@@ -7037,7 +10255,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J61">
         <f>_xlfn.LET(
@@ -7049,7 +10267,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K61">
         <f>_xlfn.LET(
@@ -7061,7 +10279,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L61">
         <f>_xlfn.LET(
@@ -7073,7 +10291,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M61">
         <f>_xlfn.LET(
@@ -7085,10 +10303,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O61" s="7">
+        <v>27</v>
+      </c>
+      <c r="P61" cm="1">
+        <f t="array" ref="P61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.30261571428571432</v>
+      </c>
+      <c r="Q61" cm="1">
+        <f t="array" ref="Q61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.40449571428571435</v>
+      </c>
+      <c r="R61" cm="1">
+        <f t="array" ref="R61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.50637571428571437</v>
+      </c>
+      <c r="S61" cm="1">
+        <f t="array" ref="S61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.60825571428571445</v>
+      </c>
+      <c r="T61" cm="1">
+        <f t="array" ref="T61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.71013571428571454</v>
+      </c>
+      <c r="U61" cm="1">
+        <f t="array" ref="U61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.8120157142857144</v>
+      </c>
+      <c r="V61" cm="1">
+        <f t="array" ref="V61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.91389571428571448</v>
+      </c>
+      <c r="W61" cm="1">
+        <f t="array" ref="W61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X61" cm="1">
+        <f t="array" ref="X61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y61" cm="1">
+        <f t="array" ref="Y61">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O61, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C62" s="7">
         <v>28</v>
       </c>
@@ -7102,7 +10443,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E62">
         <f>_xlfn.LET(
@@ -7114,7 +10455,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F62">
         <f>_xlfn.LET(
@@ -7126,7 +10467,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G62">
         <f>_xlfn.LET(
@@ -7138,7 +10479,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H62">
         <f>_xlfn.LET(
@@ -7150,7 +10491,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I62">
         <f>_xlfn.LET(
@@ -7162,7 +10503,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J62">
         <f>_xlfn.LET(
@@ -7174,7 +10515,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K62">
         <f>_xlfn.LET(
@@ -7186,7 +10527,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L62">
         <f>_xlfn.LET(
@@ -7198,7 +10539,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M62">
         <f>_xlfn.LET(
@@ -7210,10 +10551,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O62" s="7">
+        <v>28</v>
+      </c>
+      <c r="P62" cm="1">
+        <f t="array" ref="P62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + P$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.30463714285714288</v>
+      </c>
+      <c r="Q62" cm="1">
+        <f t="array" ref="Q62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Q$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.40651714285714291</v>
+      </c>
+      <c r="R62" cm="1">
+        <f t="array" ref="R62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + R$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.50839714285714288</v>
+      </c>
+      <c r="S62" cm="1">
+        <f t="array" ref="S62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + S$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.61027714285714296</v>
+      </c>
+      <c r="T62" cm="1">
+        <f t="array" ref="T62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + T$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.71215714285714304</v>
+      </c>
+      <c r="U62" cm="1">
+        <f t="array" ref="U62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + U$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.8140371428571429</v>
+      </c>
+      <c r="V62" cm="1">
+        <f t="array" ref="V62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + V$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>0.91591714285714299</v>
+      </c>
+      <c r="W62" cm="1">
+        <f t="array" ref="W62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + W$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="X62" cm="1">
+        <f t="array" ref="X62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + X$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
+      </c>
+      <c r="Y62" cm="1">
+        <f t="array" ref="Y62">_xlfn.LET(
+ _xlpm.w, MIN(MAX($O62, min_width), max_width),
+ _xlpm.normW, IF(max_width&gt;min_width,(_xlpm.w-min_width)/(max_width-min_width),0),
+ _xlpm.base, p_min + Y$35*(p_max - p_min) + flow_width_factor*_xlpm.normW,
+ _xlpm.viscScale, 0.9 + 0.4*viscosity,
+ _xlpm.viscOff, -0.05 + 0.15*viscosity,
+ _xlpm.flowRaw, _xlpm.base*flow_scale*_xlpm.viscScale + (flow_offset + _xlpm.viscOff),
+ MAX(p_min, MIN(p_max, _xlpm.flowRaw))
+)</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C63" s="7">
         <v>29</v>
       </c>
@@ -7227,7 +10691,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E63">
         <f>_xlfn.LET(
@@ -7239,7 +10703,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F63">
         <f>_xlfn.LET(
@@ -7251,7 +10715,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G63">
         <f>_xlfn.LET(
@@ -7263,7 +10727,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H63">
         <f>_xlfn.LET(
@@ -7275,7 +10739,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I63">
         <f>_xlfn.LET(
@@ -7287,7 +10751,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J63">
         <f>_xlfn.LET(
@@ -7299,7 +10763,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K63">
         <f>_xlfn.LET(
@@ -7311,7 +10775,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L63">
         <f>_xlfn.LET(
@@ -7323,7 +10787,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M63">
         <f>_xlfn.LET(
@@ -7335,10 +10799,133 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O63" s="7">
+        <v>29</v>
+      </c>
+      <c r="P63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-P$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34605876631907134</v>
+      </c>
+      <c r="Q63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-Q$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33319449875216078</v>
+      </c>
+      <c r="R63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-R$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32109598626541941</v>
+      </c>
+      <c r="S63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-S$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3098174483074827</v>
+      </c>
+      <c r="T63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-T$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.29942637538658434</v>
+      </c>
+      <c r="U63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-U$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.29001002388189978</v>
+      </c>
+      <c r="V63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-V$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.28168750056734315</v>
+      </c>
+      <c r="W63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-W$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.2746358089104618</v>
+      </c>
+      <c r="X63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-X$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.26916239545115483</v>
+      </c>
+      <c r="Y63">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C63, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-Y$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.26613665660144087</v>
       </c>
     </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C64" s="7">
         <v>30</v>
       </c>
@@ -7352,7 +10939,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.40373522737224987</v>
+        <v>0.34605876631907134</v>
       </c>
       <c r="E64">
         <f>_xlfn.LET(
@@ -7364,7 +10951,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.38872691521085417</v>
+        <v>0.33319449875216078</v>
       </c>
       <c r="F64">
         <f>_xlfn.LET(
@@ -7376,7 +10963,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.37461198397632262</v>
+        <v>0.32109598626541941</v>
       </c>
       <c r="G64">
         <f>_xlfn.LET(
@@ -7388,7 +10975,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.36145368969206315</v>
+        <v>0.3098174483074827</v>
       </c>
       <c r="H64">
         <f>_xlfn.LET(
@@ -7400,7 +10987,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.34933077128434842</v>
+        <v>0.29942637538658434</v>
       </c>
       <c r="I64">
         <f>_xlfn.LET(
@@ -7412,7 +10999,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.33834502786221637</v>
+        <v>0.29001002388189978</v>
       </c>
       <c r="J64">
         <f>_xlfn.LET(
@@ -7424,7 +11011,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32863541732856694</v>
+        <v>0.28168750056734315</v>
       </c>
       <c r="K64">
         <f>_xlfn.LET(
@@ -7436,7 +11023,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.32040844372887201</v>
+        <v>0.2746358089104618</v>
       </c>
       <c r="L64">
         <f>_xlfn.LET(
@@ -7448,7 +11035,7 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.31402279469301397</v>
+        <v>0.26916239545115483</v>
       </c>
       <c r="M64">
         <f>_xlfn.LET(
@@ -7460,12 +11047,135 @@
  _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
  MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
 )</f>
-        <v>0.3104927660350143</v>
+        <v>0.26613665660144087</v>
+      </c>
+      <c r="O64" s="7">
+        <v>30</v>
+      </c>
+      <c r="P64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-P$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.34605876631907134</v>
+      </c>
+      <c r="Q64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-Q$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.33319449875216078</v>
+      </c>
+      <c r="R64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-R$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.32109598626541941</v>
+      </c>
+      <c r="S64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-S$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.3098174483074827</v>
+      </c>
+      <c r="T64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-T$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.29942637538658434</v>
+      </c>
+      <c r="U64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-U$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.29001002388189978</v>
+      </c>
+      <c r="V64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-V$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.28168750056734315</v>
+      </c>
+      <c r="W64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-W$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.2746358089104618</v>
+      </c>
+      <c r="X64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-X$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.26916239545115483</v>
+      </c>
+      <c r="Y64">
+        <f>_xlfn.LET(
+ _xlpm.w, MIN(MAX($C64, min_width), max_width),
+ _xlpm.cone, TAN(RADIANS(spray_cone_angle/2)),
+ _xlpm.z, MIN(MAX(_xlpm.w/(2*_xlpm.cone), z_min), z_max),
+ _xlpm.sOpacity, opacity_speed_min + (1-Y$35)^opacity_gamma*(1-opacity_speed_min),
+ _xlpm.sfRaw, _xlpm.sOpacity * (z_min/_xlpm.z)^feedrate_z_exponent * (1-viscosity),
+ _xlpm.sf, MAX(0,MIN(1,_xlpm.sfRaw)),
+ MAX(feedrate_floor, v_max*_xlpm.sf) / 1524
+)</f>
+        <v>0.26613665660144087</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N29:N30">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7477,7 +11187,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36:M64">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P36:Y64">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
